--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM (7 listings)</t>
+          <t>Suzuki DS 250 SX V-STROM (2 listings)</t>
         </is>
       </c>
     </row>
@@ -553,33 +553,33 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>*SUPER RARE*  2019 Suzuki DL250X V-Strom</t>
+          <t>1997 Suzuki DS 80</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>R 59,999</t>
+          <t>R 11,900</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>29,000km</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Hermanus</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/hermanus/super-rare-2019-suzuki-dl250x-v+strom/10013432943091013436132409</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/DS/7E9F13590</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:12</t>
+          <t>02-02-2026 21:43:23</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013432943091013436132409</t>
+          <t>webuycars_7E9F13590</t>
         </is>
       </c>
     </row>
@@ -606,33 +606,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Motorcycle Suzuki Gsx 250 f</t>
+          <t>2023 Suzuki 250 DS 250</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>R 16,000</t>
+          <t>R 54,900</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>9,250km</t>
+          <t>15,999 km</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Port Elizabeth</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/port-elizabeth/motorcycle-suzuki-gsx-250-f/10013429161411010930588509</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/910309679</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -642,178 +642,132 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:12</t>
+          <t>02-02-2026 21:43:23</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013429161411010930588509</t>
+          <t>webuycars_910309679</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1997 Suzuki DS 80</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>R 13,900</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Midstream (GP)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/DS/7E9F13590</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>06-01-2026 09:50:01</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_7E9F13590</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X (11 listings)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2024 Suzuki 250 DS 250</t>
+          <t>Honda NX500</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>R 52,900</t>
+          <t>R 131,399</t>
         </is>
       </c>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>40 km</t>
+          <t>1km</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Polokwane (L)</t>
+          <t>Pinetown</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/3AEC10006</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:01</t>
+          <t>02-02-2026 21:43:46</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>webuycars_3AEC10006</t>
+          <t>gumtree_10013320405561010354228509</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2024 Suzuki 250 DS 250</t>
+          <t>2022 Honda CB500X</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>R 44,900</t>
+          <t>R 110,000</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2,500 km</t>
+          <t>8,403km</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Gqeberha (EC)</t>
+          <t>Pietermaritzburg</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/F7C213165</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2022-honda-cb500x/10013318795501012895313109</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:01</t>
+          <t>02-02-2026 21:43:48</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>webuycars_F7C213165</t>
+          <t>gumtree_10013318795501012895313109</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -823,50 +777,50 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2024 Suzuki 250 DS 250</t>
+          <t>2024 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>R 46,900</t>
+          <t>R 88,900</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>5,975 km</t>
+          <t>4,885 km</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Mbombela (MP)</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/F6EB11634</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/4BE207412</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:01</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>webuycars_F6EB11634</t>
+          <t>webuycars_4BE207412</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -876,18 +830,18 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2023 Suzuki 250 DS 250</t>
+          <t>2023 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>R 42,900</t>
+          <t>R 89,900</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>11,469 km</t>
+          <t>7,830 km</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -897,29 +851,75 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/11FD01319</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/F39C10056</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:01</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>webuycars_11FD01319</t>
+          <t>webuycars_F39C10056</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X (7 listings)</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2024 Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>R 80,900</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>11,502 km</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Dome (GP)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/513611610</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>02-02-2026 21:43:43</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_513611610</t>
         </is>
       </c>
     </row>
@@ -931,33 +931,33 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Honda NX500</t>
+          <t>2007 Honda CBR 600 RR</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>R 131,399</t>
+          <t>R 62,900</t>
         </is>
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1km</t>
+          <t>32,466 km</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/6B9613820</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:41</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013320405561010354228509</t>
+          <t>webuycars_6B9613820</t>
         </is>
       </c>
     </row>
@@ -984,33 +984,33 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2022 Honda CB500X</t>
+          <t>2015 Honda CBR 125r</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>R 110,000</t>
+          <t>R 27,900</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>8,403km</t>
+          <t>32,184 km</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg</t>
+          <t>Gqeberha (EC)</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2022-honda-cb500x/10013318795501012895313109</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9A6A00589</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:48</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013318795501012895313109</t>
+          <t>webuycars_9A6A00589</t>
         </is>
       </c>
     </row>
@@ -1042,28 +1042,28 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2024 Honda CB 500 X</t>
+          <t>2008 Honda CBR 1000 RR Fireblade</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>R 92,900</t>
+          <t>R 84,900</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>4,885 km</t>
+          <t>34,461 km</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Mbombela (MP)</t>
+          <t>Germiston (GP)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/4BE207412</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/895302815</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:29</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4BE207412</t>
+          <t>webuycars_895302815</t>
         </is>
       </c>
     </row>
@@ -1095,28 +1095,28 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2024 Honda CB 500 X</t>
+          <t>2009 Honda CBR 1000 RR Fireblade</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>R 84,900</t>
+          <t>R 79,900</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>11,502 km</t>
+          <t>52,798 km</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Mbombela (MP)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/513611610</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/DFF306975</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:29</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>webuycars_513611610</t>
+          <t>webuycars_DFF306975</t>
         </is>
       </c>
     </row>
@@ -1148,28 +1148,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2007 Honda CBR 600 RR</t>
+          <t>2009 Honda CB 600 Hornet</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>R 61,900</t>
+          <t>R 42,900</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>49,341 km</t>
+          <t>68,126 km</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/7BB005101</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/824812136</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:29</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>webuycars_7BB005101</t>
+          <t>webuycars_824812136</t>
         </is>
       </c>
     </row>
@@ -1201,28 +1201,28 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2007 Honda CBR 600 RR</t>
+          <t>2024 Honda CBR 1000rr-R</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>R 69,900</t>
+          <t>R 352,900</t>
         </is>
       </c>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>45,462 km</t>
+          <t>10,966 km</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>George (WC)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/E6ED08024</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/22E612470</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1232,72 +1232,72 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:29</t>
+          <t>02-02-2026 21:43:43</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>webuycars_E6ED08024</t>
+          <t>webuycars_22E612470</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2009 Honda CBR 1000 RR Fireblade</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>R 64,900</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>60,931 km</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>East London (EC)</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/986807218</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>06-01-2026 09:50:29</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_986807218</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400 (3 listings)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>R 109,995</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>200km</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Pinetown</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>02-02-2026 21:44:01</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10012465812701010354228509</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+          <t>2005 Kawasaki KFX 400 Quad Bike</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R 109,995</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
+          <t>R 49,950</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>200km</t>
+          <t>29,849km</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Roodepoort</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/roodepoort/2005-kawasaki-kfx-400-quad-bike/10013485328121013454052409</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1345,72 +1345,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:51:00</t>
+          <t>02-02-2026 21:44:03</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012465812701010354228509</t>
+          <t>gumtree_10013485328121013454052409</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2015 Kawasaki Ninja 300r (ex300)</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>R 38,900</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>38,993 km</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Dome (GP)</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/10B913141</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>06-01-2026 09:50:55</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_10B913141</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x (1 listings)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1420,18 +1374,18 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2010 Kawasaki Ninja 250 R</t>
+          <t>2019 Triumph Scrambler Street Scrambler</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>R 26,900</t>
+          <t>R 91,900</t>
         </is>
       </c>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>46,539 km</t>
+          <t>16,469 km</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1441,89 +1395,89 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/CDB401427</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:50:55</t>
+          <t>02-02-2026 21:44:14</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>webuycars_CDB401427</t>
+          <t>webuycars_97BD12912</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x (2 listings)</t>
+          <t>Triumph Scrambler 900 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2019 Triumph Scrambler Street Scrambler</t>
+          <t>Triumph speed twin 900</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>R 95,900</t>
+          <t>R 24,900</t>
         </is>
       </c>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>16,469 km</t>
+          <t>1,000km</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>George</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:51:20</t>
+          <t>02-02-2026 21:44:34</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>webuycars_97BD12912</t>
+          <t>gumtree_10013424411931010005469309</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1538,105 +1492,105 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>R 98,900</t>
+          <t>R 91,900</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>45,434 km</t>
+          <t>16,469 km</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>East London (EC)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/4DC912610</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:51:20</t>
+          <t>02-02-2026 21:44:31</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4DC912610</t>
+          <t>webuycars_97BD12912</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900 (3 listings)</t>
+          <t>Triumph Speed 400 (3 listings)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Triumph speed twin 900</t>
+          <t>2009 Triumph Speedmaster 865 Speedmaster EFI</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>R 25,900</t>
+          <t>R 42,900</t>
         </is>
       </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>1,000km</t>
+          <t>43,839 km</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/103713851</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:51:56</t>
+          <t>02-02-2026 21:44:46</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013424411931010005469309</t>
+          <t>webuycars_103713851</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1646,50 +1600,50 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2019 Triumph Scrambler Street Scrambler</t>
+          <t>2015 Triumph Speedmaster 865 Speedmaster EFI</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>R 95,900</t>
+          <t>R 46,900</t>
         </is>
       </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>16,469 km</t>
+          <t>50,543 km</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/AA5A00028</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:51:48</t>
+          <t>02-02-2026 21:44:46</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>webuycars_97BD12912</t>
+          <t>webuycars_AA5A00028</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1699,170 +1653,170 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2019 Triumph Scrambler Street Scrambler</t>
+          <t>2022 Triumph Speed Triple RS</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>R 98,900</t>
+          <t>R 177,900</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>45,434 km</t>
+          <t>17,155 km</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/4DC912610</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/E05B01946</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:51:48</t>
+          <t>02-02-2026 21:44:46</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4DC912610</t>
+          <t>webuycars_E05B01946</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Triumph Speed 400 (2 listings)</t>
+          <t>yamaha xsr 700 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>yamaha xsr 700</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2022 Triumph Speed Triple RS</t>
+          <t>Yamaha raptor 700</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>R 189,900</t>
+          <t>R 76,900</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>17,155 km</t>
+          <t>6km</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Thabazimbi</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/E05B01946</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/thabazimbi/yamaha-raptor-700/10013461863741013316472309</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>yamaha xsr 700</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:52:13</t>
+          <t>02-02-2026 21:45:06</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>webuycars_E05B01946</t>
+          <t>gumtree_10013461863741013316472309</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>yamaha xsr 700</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2015 Triumph Speedmaster 865 Speedmaster EFI</t>
+          <t>2016 xsr 700 Yamaha</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>R 110,000</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>50,543 km</t>
+          <t>29,560km</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>Mosselbaai</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/AA5A00028</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/mosselbaai/2016-xsr-700-yamaha/10013466040191011073853909</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>yamaha xsr 700</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:52:13</t>
+          <t>02-02-2026 21:45:03</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>webuycars_AA5A00028</t>
+          <t>gumtree_10013466040191011073853909</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>yamaha xsr 700 (2 listings)</t>
+          <t>Ducati Scrambler (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Ducati Scrambler</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1872,50 +1826,50 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2021 Yamaha Tenere 700 XTZ 700</t>
+          <t>2015 Ducati X Scrambler @Bike Bros Motorcycles!</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>R 195,000</t>
+          <t>R 124,500</t>
         </is>
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>13,100km</t>
+          <t>11,349km</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Retreat</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/2021-yamaha-tenere-700-xtz-700/10013444086691010762425009</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/retreat/2015-ducati-x-scrambler-64-bike-bros-motorcycles/10012503439581011067160209</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Ducati Scrambler</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:52:54</t>
+          <t>02-02-2026 21:45:20</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013444086691010762425009</t>
+          <t>gumtree_10012503439581011067160209</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Ducati Scrambler</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -1925,57 +1879,57 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Yamaha Raptor 700</t>
+          <t>Ducati Scrambler 800 Urban Enduro 2015</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>R 69,999</t>
+          <t>R 124,000</t>
         </is>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2,500km</t>
+          <t>11,100km</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Vereeniging</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vereeniging/yamaha-raptor-700/10013449907441010410536609</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/other/ducati-scrambler-800-urban-enduro-2015/10013434253351010003065109</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Ducati Scrambler</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:52:54</t>
+          <t>02-02-2026 21:45:20</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013449907441010410536609</t>
+          <t>gumtree_10013434253351010003065109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Ducati Scrambler (2 listings)</t>
+          <t>Yamaha MT 07 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Yamaha MT 07</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -1985,110 +1939,110 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2015 Ducati X Scrambler @Bike Bros Motorcycles!</t>
+          <t>2025 Yamaha MT07 - MT 07 NEW</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>R 124,500</t>
+          <t>R 179,950</t>
         </is>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>11,349km</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Retreat</t>
+          <t>Kraaifontein</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/retreat/2015-ducati-x-scrambler-64-bike-bros-motorcycles/10012503439581011067160209</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kraaifontein/2025-yamaha-mt07-+-mt-07-new/10013416804491010004286409</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Yamaha MT 07</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:21</t>
+          <t>02-02-2026 21:45:27</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012503439581011067160209</t>
+          <t>gumtree_10013416804491010004286409</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Yamaha MT 07</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler 800 Urban Enduro 2015</t>
+          <t>2018 Yamaha MT MT-09 Tracer</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>R 124,900</t>
+          <t>R 114,900</t>
         </is>
       </c>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>11,100km</t>
+          <t>11,998 km</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/other/ducati-scrambler-800-urban-enduro-2015/10013434253351010003065109</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Yamaha/MT/4F9108269</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Yamaha MT 07</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:21</t>
+          <t>02-02-2026 21:45:26</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013434253351010003065109</t>
+          <t>webuycars_4F9108269</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Yamaha MT 07 (4 listings)</t>
+          <t>BMW G 310 (8 listings)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2098,156 +2052,156 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>2025 Yamaha MT07 - MT 07 NEW</t>
+          <t>2018 BMW 310 / 45 / G450</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>R 179,950</t>
+          <t>R 45,000</t>
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>32,500km</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Kraaifontein</t>
+          <t>Vanderbijlpark</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kraaifontein/2025-yamaha-mt07-+-mt-07-new/10013416804491010004286409</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vanderbijlpark/2018-bmw-310-45-g450/10013459591011011119609209</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:33</t>
+          <t>02-02-2026 21:45:43</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013416804491010004286409</t>
+          <t>gumtree_10013459591011011119609209</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2021 Yamaha MT MT-09 Tracer</t>
+          <t>2018 BMW G310 GS</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>R 89,900</t>
+          <t>R 55,000</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>62,115 km</t>
+          <t>7,353km</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>Pietermaritzburg</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Yamaha/MT/81FC13849</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2018-bmw-g310-gs/10013465574691012895313109</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:25</t>
+          <t>02-02-2026 21:45:44</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>webuycars_81FC13849</t>
+          <t>gumtree_10013465574691012895313109</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2021 Yamaha MT Tenere 700 (xtz690)</t>
+          <t>BMW 310</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>R 159,900</t>
+          <t>R 69,500</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>6,740 km</t>
+          <t>17,000km</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Montague Gardens</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Yamaha/MT/73F808904</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/montague-gardens/bmw-310/10013251672391010002889209</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:25</t>
+          <t>02-02-2026 21:45:43</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>webuycars_73F808904</t>
+          <t>gumtree_10013251672391010002889209</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -2257,50 +2211,96 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>2018 Yamaha MT MT-09 Tracer</t>
+          <t>2022 BMW G Series G 310 R</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>R 114,900</t>
+          <t>R 43,900</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>11,998 km</t>
+          <t>22,490 km</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Riverhorse (KZN)</t>
+          <t>Silver Lakes (GP)</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Yamaha/MT/4F9108269</t>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/9DB310327</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>BMW G 310</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:25</t>
+          <t>02-02-2026 21:45:40</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4F9108269</t>
+          <t>webuycars_9DB310327</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>BMW G 310 (4 listings)</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2015 BMW G Series G650 GS ABS H/grips</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>R 64,900</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>33,076 km</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Brackenfell (WC)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/866314815</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>02-02-2026 21:45:40</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_866314815</t>
         </is>
       </c>
     </row>
@@ -2312,33 +2312,33 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW 310 / 45 / G450</t>
+          <t>2008 BMW G Series G450 X</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>R 45,000</t>
+          <t>R 32,900</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>32,500km</t>
+          <t>8,076 km</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Vanderbijlpark</t>
+          <t>Montana (GP)</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vanderbijlpark/2018-bmw-310-45-g450/10013459591011011119609209</t>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/76DE04781</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:56</t>
+          <t>02-02-2026 21:45:40</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013459591011011119609209</t>
+          <t>webuycars_76DE04781</t>
         </is>
       </c>
     </row>
@@ -2370,28 +2370,28 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>2022 BMW G Series G 310 R</t>
+          <t>2012 BMW G Series G650 GS</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>R 49,900</t>
+          <t>R 56,900</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>22,490 km</t>
+          <t>34,097 km</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>Germiston (GP)</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/9DB310327</t>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/8DF302214</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:47</t>
+          <t>02-02-2026 21:45:40</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9DB310327</t>
+          <t>webuycars_8DF302214</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>R 37,900</t>
+          <t>R 31,900</t>
         </is>
       </c>
       <c r="E46" s="4" t="n"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:53:47</t>
+          <t>02-02-2026 21:45:40</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -2464,62 +2464,62 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>2008 BMW G Series G 650 X Cntry ABS</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>24,813 km</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Brackenfell (WC)</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/5DFF00161</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>06-01-2026 09:53:47</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_5DFF00161</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>BMW GS 310 (3 listings)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>BMW GS 310 (1 listings)</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2018 BMW 310 / 45 / G450</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>R 45,000</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>32,500km</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Vanderbijlpark</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vanderbijlpark/2018-bmw-310-45-g450/10013459591011011119609209</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>02-02-2026 21:45:55</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013459591011011119609209</t>
         </is>
       </c>
     </row>
@@ -2536,28 +2536,28 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW 310 / 45 / G450</t>
+          <t>2018 BMW G310 GS</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>R 45,000</t>
+          <t>R 55,000</t>
         </is>
       </c>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>32,500km</t>
+          <t>7,353km</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Vanderbijlpark</t>
+          <t>Pietermaritzburg</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vanderbijlpark/2018-bmw-310-45-g450/10013459591011011119609209</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2018-bmw-g310-gs/10013465574691012895313109</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2567,72 +2567,72 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:54:13</t>
+          <t>02-02-2026 21:45:56</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013459591011011119609209</t>
+          <t>gumtree_10013465574691012895313109</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400 (6 listings)</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>BMW 310</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>R 69,500</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>17,000km</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Montague Gardens</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/montague-gardens/bmw-310/10013251672391010002889209</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>02-02-2026 21:45:57</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013251672391010002889209</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>R 109,995</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>200km</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Pinetown</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>06-01-2026 09:54:41</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10012465812701010354228509</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400 (4 listings)</t>
         </is>
       </c>
     </row>
@@ -2644,33 +2644,33 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2016 Kawasaki Zx10 Zx10-R</t>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>R 141,000</t>
+          <t>R 109,995</t>
         </is>
       </c>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>21,878 km</t>
+          <t>200km</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Mbombela (MP)</t>
+          <t>Pinetown</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Zx10/0FB705702</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:54:35</t>
+          <t>02-02-2026 21:46:12</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>webuycars_0FB705702</t>
+          <t>gumtree_10012465812701010354228509</t>
         </is>
       </c>
     </row>
@@ -2697,33 +2697,33 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>2008 Kawasaki ZX 14</t>
+          <t>2005 Kawasaki KFX 400 Quad Bike</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>R 68,900</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n"/>
+          <t>R 49,950</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>69,086 km</t>
+          <t>29,849km</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Germiston (GP)</t>
+          <t>Roodepoort</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/AAA711971</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/roodepoort/2005-kawasaki-kfx-400-quad-bike/10013485328121013454052409</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:54:35</t>
+          <t>02-02-2026 21:46:12</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>webuycars_AAA711971</t>
+          <t>gumtree_10013485328121013454052409</t>
         </is>
       </c>
     </row>
@@ -2755,28 +2755,28 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>2022 Kawasaki Z 900 ABS (zr900f)</t>
+          <t>2007 Kawasaki ZX 14</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>R 139,900</t>
+          <t>R 75,900</t>
         </is>
       </c>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>10,732 km</t>
+          <t>43,595 km</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Z 900/031302389</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/F5BC02354</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:54:35</t>
+          <t>02-02-2026 21:46:08</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>webuycars_031302389</t>
+          <t>webuycars_F5BC02354</t>
         </is>
       </c>
     </row>
@@ -2808,28 +2808,28 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>2021 Kawasaki Z 900 ABS (zr900f)</t>
+          <t>2013 Kawasaki ZX Zx10-R</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>R 129,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>10,227 km</t>
+          <t>49,266 km</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>JHB South (GP)</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Z 900/28B610027</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/D5ED16783</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -2839,142 +2839,89 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>06-01-2026 09:54:35</t>
+          <t>02-02-2026 21:46:08</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>webuycars_28B610027</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>2009 Kawasaki ZX6-R ZX 6R</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>99,281 km</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>Dome (GP)</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX6-R/728E14813</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>06-01-2026 09:54:35</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_728E14813</t>
+          <t>webuycars_D5ED16783</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>SUMMARY</t>
-        </is>
+          <t>Total Listings:</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Total Listings:</t>
+          <t>Bikes Tracked:</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Bikes Tracked:</t>
+          <t>Sources:</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Sources:</t>
+          <t>Price Drops Detected:</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Price Drops Detected:</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
           <t>Last Updated:</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>06/01/2026 09:55:01</t>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>02/02/2026 21:46:28</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A18:K18"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A47:K47"/>
     <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:23</t>
+          <t>03-02-2026 12:14:45</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:23</t>
+          <t>03-02-2026 12:14:45</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:46</t>
+          <t>03-02-2026 12:15:11</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:48</t>
+          <t>03-02-2026 12:15:13</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:43:43</t>
+          <t>03-02-2026 12:15:06</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:01</t>
+          <t>03-02-2026 12:15:25</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1322,7 +1322,7 @@
           <t>R 49,950</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>29,849km</t>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:03</t>
+          <t>03-02-2026 12:15:28</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:14</t>
+          <t>03-02-2026 12:15:39</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:34</t>
+          <t>03-02-2026 12:16:08</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:31</t>
+          <t>03-02-2026 12:16:03</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:46</t>
+          <t>03-02-2026 12:16:18</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:46</t>
+          <t>03-02-2026 12:16:18</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:44:46</t>
+          <t>03-02-2026 12:16:18</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -1713,28 +1713,28 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Yamaha raptor 700</t>
+          <t>2016 xsr 700 Yamaha</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>R 76,900</t>
+          <t>R 110,000</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>6km</t>
+          <t>29,560km</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Thabazimbi</t>
+          <t>Mosselbaai</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/thabazimbi/yamaha-raptor-700/10013461863741013316472309</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/mosselbaai/2016-xsr-700-yamaha/10013466040191011073853909</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:06</t>
+          <t>03-02-2026 12:16:38</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013461863741013316472309</t>
+          <t>gumtree_10013466040191011073853909</t>
         </is>
       </c>
     </row>
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2016 xsr 700 Yamaha</t>
+          <t>Yamaha raptor 700</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>R 110,000</t>
+          <t>R 76,900</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>29,560km</t>
+          <t>6km</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Mosselbaai</t>
+          <t>Thabazimbi</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/mosselbaai/2016-xsr-700-yamaha/10013466040191011073853909</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/thabazimbi/yamaha-raptor-700/10013461863741013316472309</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:03</t>
+          <t>03-02-2026 12:16:40</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013466040191011073853909</t>
+          <t>gumtree_10013461863741013316472309</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:20</t>
+          <t>03-02-2026 12:16:52</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:20</t>
+          <t>03-02-2026 12:16:52</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:27</t>
+          <t>03-02-2026 12:16:59</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:26</t>
+          <t>03-02-2026 12:16:57</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:43</t>
+          <t>03-02-2026 12:17:17</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -2105,28 +2105,28 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW G310 GS</t>
+          <t>BMW 310</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>R 55,000</t>
+          <t>R 69,500</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>7,353km</t>
+          <t>17,000km</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg</t>
+          <t>Montague Gardens</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2018-bmw-g310-gs/10013465574691012895313109</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/montague-gardens/bmw-310/10013251672391010002889209</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:44</t>
+          <t>03-02-2026 12:17:17</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013465574691012895313109</t>
+          <t>gumtree_10013251672391010002889209</t>
         </is>
       </c>
     </row>
@@ -2158,28 +2158,28 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>BMW 310</t>
+          <t>2018 BMW G310 GS</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>R 69,500</t>
+          <t>R 55,000</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>17,000km</t>
+          <t>7,353km</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Montague Gardens</t>
+          <t>Pietermaritzburg</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/montague-gardens/bmw-310/10013251672391010002889209</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2018-bmw-g310-gs/10013465574691012895313109</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:43</t>
+          <t>03-02-2026 12:17:19</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013251672391010002889209</t>
+          <t>gumtree_10013465574691012895313109</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:40</t>
+          <t>03-02-2026 12:17:13</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:40</t>
+          <t>03-02-2026 12:17:13</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:40</t>
+          <t>03-02-2026 12:17:13</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:40</t>
+          <t>03-02-2026 12:17:13</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:40</t>
+          <t>03-02-2026 12:17:13</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:55</t>
+          <t>03-02-2026 12:17:30</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:56</t>
+          <t>03-02-2026 12:17:32</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:45:57</t>
+          <t>03-02-2026 12:17:33</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:46:12</t>
+          <t>03-02-2026 12:17:48</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -2710,7 +2710,7 @@
           <t>R 49,950</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>29,849km</t>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:46:12</t>
+          <t>03-02-2026 12:17:48</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:46:08</t>
+          <t>03-02-2026 12:17:44</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>02-02-2026 21:46:08</t>
+          <t>03-02-2026 12:17:44</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>02/02/2026 21:46:28</t>
+          <t>03/02/2026 12:18:05</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -541,14 +541,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM (2 listings)</t>
+          <t>Suzuki V-STROM 250 SX (1 listings)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Suzuki V-STROM 250 SX</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -558,18 +558,18 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>1997 Suzuki DS 80</t>
+          <t>2023 Suzuki 250 DS 250</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>R 11,900</t>
+          <t>R 51,900</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>15,999 km</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -579,82 +579,82 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/DS/7E9F13590</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/910309679</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
+          <t>Suzuki V-STROM 250 SX</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:14:45</t>
+          <t>20-02-2026 10:35:18</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>webuycars_7E9F13590</t>
+          <t>webuycars_910309679</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2023 Suzuki 250 DS 250</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>R 54,900</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>15,999 km</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Midstream (GP)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/910309679</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Suzuki DS 250 SX V-STROM</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:14:45</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_910309679</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X (11 listings)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X (11 listings)</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Honda NX500</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>R 131,399</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1km</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Pinetown</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:36:04</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013320405561010354228509</t>
         </is>
       </c>
     </row>
@@ -671,28 +671,28 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Honda NX500</t>
+          <t>2022 Honda CB500X</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>R 131,399</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
+          <t>R 105,000</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1km</t>
+          <t>8,403km</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Pietermaritzburg</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2022-honda-cb500x/10013318795501012895313109</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:11</t>
+          <t>20-02-2026 10:36:07</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013320405561010354228509</t>
+          <t>gumtree_10013318795501012895313109</t>
         </is>
       </c>
     </row>
@@ -724,28 +724,28 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2022 Honda CB500X</t>
+          <t>2023 Honda CB500x</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>R 110,000</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>R 102,500</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>8,403km</t>
+          <t>2,400km</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg</t>
+          <t>Hermanus</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2022-honda-cb500x/10013318795501012895313109</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/hermanus/2023-honda-cb500x/10013489373131010967088109</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:13</t>
+          <t>20-02-2026 10:36:07</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013318795501012895313109</t>
+          <t>gumtree_10013489373131010967088109</t>
         </is>
       </c>
     </row>
@@ -772,33 +772,33 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2024 Honda CB 500 X</t>
+          <t>Honda CB500XA</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>R 88,900</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
+          <t>R 95,000</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>4,885 km</t>
+          <t>6,100km</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Mbombela (MP)</t>
+          <t>Cape Agulhas</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/4BE207412</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/cape-agulhas/honda-cb500xa/10013437062981010011219209</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:36:07</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4BE207412</t>
+          <t>gumtree_10013437062981010011219209</t>
         </is>
       </c>
     </row>
@@ -830,18 +830,18 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2023 Honda CB 500 X</t>
+          <t>2024 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>R 89,900</t>
+          <t>R 76,900</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>7,830 km</t>
+          <t>11,502 km</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/F39C10056</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/513611610</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>webuycars_F39C10056</t>
+          <t>webuycars_513611610</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2024 Honda CB 500 X</t>
+          <t>2015 Honda CBR 125r</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>R 80,900</t>
+          <t>R 23,900</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>11,502 km</t>
+          <t>32,184 km</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Gqeberha (EC)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/513611610</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9A6A00589</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>webuycars_513611610</t>
+          <t>webuycars_9A6A00589</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>R 62,900</t>
+          <t>R 58,900</t>
         </is>
       </c>
       <c r="E11" s="4" t="n"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -989,28 +989,28 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2015 Honda CBR 125r</t>
+          <t>2008 Honda CBR 1000 RR Fireblade</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>R 27,900</t>
+          <t>R 80,900</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>32,184 km</t>
+          <t>34,461 km</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Gqeberha (EC)</t>
+          <t>Germiston (GP)</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9A6A00589</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/895302815</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9A6A00589</t>
+          <t>webuycars_895302815</t>
         </is>
       </c>
     </row>
@@ -1042,28 +1042,28 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2008 Honda CBR 1000 RR Fireblade</t>
+          <t>2009 Honda CB 600 Hornet</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>R 84,900</t>
+          <t>R 39,900</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>34,461 km</t>
+          <t>68,126 km</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Germiston (GP)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/895302815</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/824812136</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>webuycars_895302815</t>
+          <t>webuycars_824812136</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>R 79,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>52,798 km</t>
+          <t>74,208 km</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Mbombela (MP)</t>
+          <t>Silver Lakes (GP)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/DFF306975</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9E0302015</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>webuycars_DFF306975</t>
+          <t>webuycars_9E0302015</t>
         </is>
       </c>
     </row>
@@ -1148,28 +1148,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2009 Honda CB 600 Hornet</t>
+          <t>2024 Honda CBR 1000rr-R</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>R 42,900</t>
+          <t>R 352,900</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>68,126 km</t>
+          <t>10,966 km</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>George (WC)</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/824812136</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/22E612470</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:06</t>
+          <t>20-02-2026 10:35:59</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>webuycars_824812136</t>
+          <t>webuycars_22E612470</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2024 Honda CBR 1000rr-R</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>R 352,900</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>10,966 km</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>George (WC)</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/22E612470</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:15:06</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_22E612470</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400 (3 listings)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400 (2 listings)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>R 109,995</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>200km</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Pinetown</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:36:21</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10012465812701010354228509</t>
         </is>
       </c>
     </row>
@@ -1261,28 +1261,28 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+          <t>Zzr 400 kawasaki</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>R 109,995</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
+          <t>R 7,500</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>200km</t>
+          <t>123,456km</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Kroonstad</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kroonstad/zzr-400-kawasaki/10013493850161013085967409</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:25</t>
+          <t>20-02-2026 10:36:24</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012465812701010354228509</t>
+          <t>gumtree_10013493850161013085967409</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2005 Kawasaki KFX 400 Quad Bike</t>
+          <t>2019 Kawasaki Ninja 650 (ex650) ABS</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R 49,950</t>
+          <t>R 72,900</t>
         </is>
       </c>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>29,849km</t>
+          <t>19,765 km</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Roodepoort</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/roodepoort/2005-kawasaki-kfx-400-quad-bike/10013485328121013454052409</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/67E900160</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1345,305 +1345,305 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:28</t>
+          <t>20-02-2026 10:36:19</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013485328121013454052409</t>
+          <t>webuycars_67E900160</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x (1 listings)</t>
+          <t>suzuki Gixxer 250 (3 listings)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>suzuki Gixxer 250</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2019 Triumph Scrambler Street Scrambler</t>
+          <t>2024 Suzuki Gixxer 250 Cc (2nd Owner Since New)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>R 91,900</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
+          <t>R 42,500</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>16,469 km</t>
+          <t>4,200km</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Johannesburg South</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/2024-suzuki-gixxer-250-cc-2nd-owner-since-new/10013496103141012587794309</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>suzuki Gixxer 250</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:15:39</t>
+          <t>20-02-2026 10:36:36</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>webuycars_97BD12912</t>
+          <t>gumtree_10013496103141012587794309</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900 (2 listings)</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki Gixxer Naked 250fi</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>R 45,000</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>3,500km</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Muizenberg</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/muizenberg/suzuki-gixxer-naked-250fi/10013392378371010784220709</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:36:37</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013392378371010784220709</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>suzuki Gixxer 250</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Triumph speed twin 900</t>
+          <t>2023 Suzuki 250 DS 250</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>R 24,900</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n"/>
+          <t>R 51,900</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>1,000km</t>
+          <t>15,999 km</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/910309679</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>suzuki Gixxer 250</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:16:08</t>
+          <t>20-02-2026 10:36:35</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013424411931010005469309</t>
+          <t>webuycars_910309679</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x (1 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>2019 Triumph Scrambler Street Scrambler</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>R 91,900</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>16,469 km</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>East London (EC)</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:16:03</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:36:50</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>webuycars_97BD12912</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Triumph Speed 400 (3 listings)</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Speed 400</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>2009 Triumph Speedmaster 865 Speedmaster EFI</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>R 42,900</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>43,839 km</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Midstream (GP)</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/103713851</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Speed 400</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:16:18</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_103713851</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2015 Triumph Speedmaster 865 Speedmaster EFI</t>
+          <t>Triumph speed twin 900</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>R 46,900</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
+          <t>R 24,900</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>50,543 km</t>
+          <t>1,000km</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>George</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/AA5A00028</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:16:18</t>
+          <t>20-02-2026 10:37:13</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>webuycars_AA5A00028</t>
+          <t>gumtree_10013424411931010005469309</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1653,216 +1653,216 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2022 Triumph Speed Triple RS</t>
+          <t>2019 Triumph Scrambler Street Scrambler</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>R 177,900</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n"/>
+          <t>R 91,900</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>17,155 km</t>
+          <t>16,469 km</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>East London (EC)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/E05B01946</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:16:18</t>
+          <t>20-02-2026 10:37:08</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>webuycars_E05B01946</t>
+          <t>webuycars_97BD12912</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>yamaha xsr 700 (2 listings)</t>
+          <t>Triumph Speed 400 (3 listings)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2016 xsr 700 Yamaha</t>
+          <t>2009 Triumph Speedmaster 865 Speedmaster EFI</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>R 110,000</t>
+          <t>R 42,900</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>29,560km</t>
+          <t>43,839 km</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Mosselbaai</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/mosselbaai/2016-xsr-700-yamaha/10013466040191011073853909</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/103713851</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:16:38</t>
+          <t>20-02-2026 10:37:23</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013466040191011073853909</t>
+          <t>webuycars_103713851</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Yamaha raptor 700</t>
+          <t>2015 Triumph Speedmaster 865 Speedmaster EFI</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>R 76,900</t>
+          <t>R 40,900</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>6km</t>
+          <t>50,543 km</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Thabazimbi</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/thabazimbi/yamaha-raptor-700/10013461863741013316472309</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/AA5A00028</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>yamaha xsr 700</t>
+          <t>Triumph Speed 400</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:16:40</t>
+          <t>20-02-2026 10:37:23</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013461863741013316472309</t>
+          <t>webuycars_AA5A00028</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Ducati Scrambler (2 listings)</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2022 Triumph Speed Triple RS</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>R 171,900</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>17,155 km</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/E05B01946</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:37:23</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_E05B01946</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Ducati Scrambler</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>2015 Ducati X Scrambler @Bike Bros Motorcycles!</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>R 124,500</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>11,349km</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Retreat</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/retreat/2015-ducati-x-scrambler-64-bike-bros-motorcycles/10012503439581011067160209</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>Ducati Scrambler</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:16:52</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10012503439581011067160209</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler (3 listings)</t>
         </is>
       </c>
     </row>
@@ -1879,216 +1879,216 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
+          <t>2015 Ducati X Scrambler @Bike Bros Motorcycles!</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>R 124,500</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>11,349km</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Retreat</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/retreat/2015-ducati-x-scrambler-64-bike-bros-motorcycles/10012503439581011067160209</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:37:58</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10012503439581011067160209</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
           <t>Ducati Scrambler 800 Urban Enduro 2015</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>R 124,000</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>11,100km</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>https://www.gumtree.co.za/a-motorcycles-scooters/other/ducati-scrambler-800-urban-enduro-2015/10013434253351010003065109</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Ducati Scrambler</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:16:52</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:37:58</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>gumtree_10013434253351010003065109</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Yamaha MT 07 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>Ducati Scrambler</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2025 Yamaha MT07 - MT 07 NEW</t>
+          <t>2015 Ducati Scrambler Icon RED</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>R 179,950</t>
+          <t>R 54,900</t>
         </is>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
+          <t>55,001 km</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Ducati/Scrambler/7C2A03344</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:37:56</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_7C2A03344</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07 (1 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2025 Yamaha MT07 - MT 07 NEW</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>R 179,950</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Kraaifontein</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>https://www.gumtree.co.za/a-motorcycles-scooters/kraaifontein/2025-yamaha-mt07-+-mt-07-new/10013416804491010004286409</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>Yamaha MT 07</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:16:59</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:38:03</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>gumtree_10013416804491010004286409</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Yamaha MT 07</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>2018 Yamaha MT MT-09 Tracer</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>R 114,900</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>11,998 km</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Dome (GP)</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Yamaha/MT/4F9108269</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Yamaha MT 07</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:16:57</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_4F9108269</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>BMW G 310 (8 listings)</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>2018 BMW 310 / 45 / G450</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>R 45,000</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>32,500km</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Vanderbijlpark</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vanderbijlpark/2018-bmw-310-45-g450/10013459591011011119609209</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:17:17</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013459591011011119609209</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>BMW G 310 (5 listings)</t>
         </is>
       </c>
     </row>
@@ -2105,28 +2105,28 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>BMW 310</t>
+          <t>BMW G310R 2022</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>R 69,500</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n"/>
+          <t>R 55,000</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>17,000km</t>
+          <t>5,740km</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Montague Gardens</t>
+          <t>Chatsworth</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/montague-gardens/bmw-310/10013251672391010002889209</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/chatsworth/bmw-g310r-2022/10013491315601011124314909</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:17</t>
+          <t>20-02-2026 10:38:23</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013251672391010002889209</t>
+          <t>gumtree_10013491315601011124314909</t>
         </is>
       </c>
     </row>
@@ -2158,28 +2158,28 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW G310 GS</t>
+          <t>2020 BMW G310R</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>R 55,000</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n"/>
+          <t>R 54,000</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>7,353km</t>
+          <t>20,404km</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg</t>
+          <t>Strand</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2018-bmw-g310-gs/10013465574691012895313109</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/strand/2020-bmw-g310r/10013500017401010054138109</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:19</t>
+          <t>20-02-2026 10:38:23</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013465574691012895313109</t>
+          <t>gumtree_10013500017401010054138109</t>
         </is>
       </c>
     </row>
@@ -2211,28 +2211,28 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>2022 BMW G Series G 310 R</t>
+          <t>2015 BMW G Series G650 GS ABS H/grips</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>R 43,900</t>
+          <t>R 65,900</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>22,490 km</t>
+          <t>33,076 km</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>Brackenfell (WC)</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/9DB310327</t>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/866314815</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:13</t>
+          <t>20-02-2026 10:38:17</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9DB310327</t>
+          <t>webuycars_866314815</t>
         </is>
       </c>
     </row>
@@ -2264,28 +2264,28 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2015 BMW G Series G650 GS ABS H/grips</t>
+          <t>2008 BMW G Series G450 X</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>R 64,900</t>
+          <t>R 29,900</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>33,076 km</t>
+          <t>8,076 km</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Brackenfell (WC)</t>
+          <t>Montana (GP)</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/866314815</t>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/76DE04781</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:13</t>
+          <t>20-02-2026 10:38:17</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>webuycars_866314815</t>
+          <t>webuycars_76DE04781</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2008 BMW G Series G450 X</t>
+          <t>2014 BMW G Series G 650 GS Sertao ABS H/grips</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>R 32,900</t>
+          <t>R 24,900</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>8,076 km</t>
+          <t>73,328 km</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Montana (GP)</t>
+          <t>George (WC)</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/76DE04781</t>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/CAF414786</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -2348,132 +2348,86 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:13</t>
+          <t>20-02-2026 10:38:17</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>webuycars_76DE04781</t>
+          <t>webuycars_CAF414786</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>2012 BMW G Series G650 GS</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>R 56,900</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>34,097 km</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Germiston (GP)</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/8DF302214</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:17:13</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_8DF302214</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>BMW GS 310 (1 listings)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>BMW GS 310</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2014 BMW G Series G 650 GS Sertao ABS H/grips</t>
+          <t>2019 BMW R 310 GS 5015km only</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>R 31,900</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n"/>
+          <t>R 62,000</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>73,328 km</t>
+          <t>5,015km</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>George (WC)</t>
+          <t>Langebaan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/CAF414786</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/langebaan/2019-bmw-r-310-gs-5015km-only/10013489014211010017154009</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>BMW GS 310</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:13</t>
+          <t>20-02-2026 10:38:35</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>webuycars_CAF414786</t>
+          <t>gumtree_10013489014211010017154009</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>BMW GS 310 (3 listings)</t>
+          <t>Kawasaki Z 400 (4 listings)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Kawasaki Z 400</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -2483,50 +2437,50 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW 310 / 45 / G450</t>
+          <t>Zzr 400 kawasaki</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>R 45,000</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n"/>
+          <t>R 7,500</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>32,500km</t>
+          <t>123,456km</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Vanderbijlpark</t>
+          <t>Kroonstad</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/vanderbijlpark/2018-bmw-310-45-g450/10013459591011011119609209</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kroonstad/zzr-400-kawasaki/10013493850161013085967409</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Kawasaki Z 400</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:30</t>
+          <t>20-02-2026 10:38:54</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013459591011011119609209</t>
+          <t>gumtree_10013493850161013085967409</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Kawasaki Z 400</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -2536,392 +2490,226 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW G310 GS</t>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>R 55,000</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n"/>
+          <t>R 109,995</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>7,353km</t>
+          <t>200km</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg</t>
+          <t>Pinetown</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2018-bmw-g310-gs/10013465574691012895313109</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Kawasaki Z 400</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:32</t>
+          <t>20-02-2026 10:38:54</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013465574691012895313109</t>
+          <t>gumtree_10012465812701010354228509</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Kawasaki Z 400</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BMW 310</t>
+          <t>2007 Kawasaki ZX 14</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>R 69,500</t>
+          <t>R 71,900</t>
         </is>
       </c>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>17,000km</t>
+          <t>43,595 km</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Montague Gardens</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/montague-gardens/bmw-310/10013251672391010002889209</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/F5BC02354</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Kawasaki Z 400</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>03-02-2026 12:17:33</t>
+          <t>20-02-2026 10:38:49</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013251672391010002889209</t>
+          <t>webuycars_F5BC02354</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400 (4 listings)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Kawasaki Z 400</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>R 109,995</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>200km</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Pinetown</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2007 Kawasaki ZX 14</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>R 64,900</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>61,929 km</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Brackenfell (WC)</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/D21303206</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>Kawasaki Z 400</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:17:48</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10012465812701010354228509</t>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>20-02-2026 10:38:49</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_D21303206</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>2005 Kawasaki KFX 400 Quad Bike</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>R 49,950</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>29,849km</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Roodepoort</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/roodepoort/2005-kawasaki-kfx-400-quad-bike/10013485328121013454052409</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:17:48</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013485328121013454052409</t>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>2007 Kawasaki ZX 14</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>R 75,900</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>43,595 km</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Richmond (WC)</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/F5BC02354</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:17:44</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_F5BC02354</t>
-        </is>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Total Listings:</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>2013 Kawasaki ZX Zx10-R</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>49,266 km</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Midstream (GP)</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/D5ED16783</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:17:44</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_D5ED16783</t>
-        </is>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Bikes Tracked:</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Sources:</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>SUMMARY</t>
-        </is>
+          <t>Price Drops Detected:</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Total Listings:</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Bikes Tracked:</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Sources:</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Price Drops Detected:</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
           <t>Last Updated:</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>03/02/2026 12:18:05</t>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>20/02/2026 10:39:12</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A4:K4"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A33:K33"/>
     <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A53:B53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Suzuki V-STROM 250 SX (1 listings)</t>
+          <t>Suzuki V-STROM 250 SX (2 listings)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
           <t>R 51,900</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>15,999 km</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:18</t>
+          <t>22-02-2026 10:59:14</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -599,221 +599,175 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X (11 listings)</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki V-STROM 250 SX</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1992 Suzuki RGV 250</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>R99,990</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>30,201km</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/1992-suzuki-rgv-250/</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki V-STROM 250 SX</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 10:59:14</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_1992-suzuki-rgv-250</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Honda NX500</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>R 131,399</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1km</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Pinetown</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>20-02-2026 10:36:04</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013320405561010354228509</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Lifan X Trail 250 (2 listings)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Honda CB 500 X</t>
+          <t>Lifan X Trail 250</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2022 Honda CB500X</t>
+          <t>2025 Lifan X-Trail 250</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>R 105,000</t>
+          <t>R26,990</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>8,403km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2022-honda-cb500x/10013318795501012895313109</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-lifan-x-trail-250-2/</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Honda CB 500 X</t>
+          <t>Lifan X Trail 250</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:07</t>
+          <t>22-02-2026 10:59:38</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013318795501012895313109</t>
+          <t>zabikers_2025-lifan-x-trail-250-2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Honda CB 500 X</t>
+          <t>Lifan X Trail 250</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2023 Honda CB500x</t>
+          <t>2025 Lifan X-Trail 250</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>R 102,500</t>
+          <t>R26,990</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2,400km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Hermanus</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/hermanus/2023-honda-cb500x/10013489373131010967088109</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-lifan-x-trail-250/</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Honda CB 500 X</t>
+          <t>Lifan X Trail 250</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:07</t>
+          <t>22-02-2026 10:59:38</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013489373131010967088109</t>
+          <t>zabikers_2025-lifan-x-trail-250</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB500XA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>R 95,000</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>6,100km</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Cape Agulhas</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/cape-agulhas/honda-cb500xa/10013437062981010011219209</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Honda CB 500 X</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>20-02-2026 10:36:07</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013437062981010011219209</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X (20 listings)</t>
         </is>
       </c>
     </row>
@@ -825,33 +779,33 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2024 Honda CB 500 X</t>
+          <t>Honda NX500</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>R 76,900</t>
+          <t>R 131,399</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>11,502 km</t>
+          <t>1km</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Pinetown</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/513611610</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -861,12 +815,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 11:00:03</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>webuycars_513611610</t>
+          <t>gumtree_10013320405561010354228509</t>
         </is>
       </c>
     </row>
@@ -878,33 +832,33 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2015 Honda CBR 125r</t>
+          <t>2022 Honda CB500X</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>R 23,900</t>
+          <t>R 105,000</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>32,184 km</t>
+          <t>8,403km</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Gqeberha (EC)</t>
+          <t>Pietermaritzburg</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9A6A00589</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2022-honda-cb500x/10013318795501012895313109</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -914,12 +868,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 11:00:05</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9A6A00589</t>
+          <t>gumtree_10013318795501012895313109</t>
         </is>
       </c>
     </row>
@@ -931,33 +885,33 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2007 Honda CBR 600 RR</t>
+          <t>2023 Honda CB500x</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>R 58,900</t>
+          <t>R 102,500</t>
         </is>
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>32,466 km</t>
+          <t>2,400km</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Hermanus</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/6B9613820</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/hermanus/2023-honda-cb500x/10013489373131010967088109</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -967,12 +921,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 11:00:05</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>webuycars_6B9613820</t>
+          <t>gumtree_10013489373131010967088109</t>
         </is>
       </c>
     </row>
@@ -984,33 +938,33 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2008 Honda CBR 1000 RR Fireblade</t>
+          <t>Honda CB500XA</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>R 80,900</t>
+          <t>R 95,000</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>34,461 km</t>
+          <t>6,100km</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Germiston (GP)</t>
+          <t>Cape Agulhas</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/895302815</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/cape-agulhas/honda-cb500xa/10013437062981010011219209</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1020,12 +974,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 11:00:05</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>webuycars_895302815</t>
+          <t>gumtree_10013437062981010011219209</t>
         </is>
       </c>
     </row>
@@ -1042,28 +996,28 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2009 Honda CB 600 Hornet</t>
+          <t>2024 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>R 39,900</t>
+          <t>R 76,900</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>68,126 km</t>
+          <t>11,502 km</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/824812136</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/513611610</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1073,12 +1027,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>webuycars_824812136</t>
+          <t>webuycars_513611610</t>
         </is>
       </c>
     </row>
@@ -1095,28 +1049,28 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2009 Honda CBR 1000 RR Fireblade</t>
+          <t>2015 Honda CBR 125r</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>R 23,900</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>74,208 km</t>
+          <t>32,184 km</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>Gqeberha (EC)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9E0302015</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9A6A00589</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1126,12 +1080,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9E0302015</t>
+          <t>webuycars_9A6A00589</t>
         </is>
       </c>
     </row>
@@ -1148,28 +1102,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2024 Honda CBR 1000rr-R</t>
+          <t>2007 Honda CBR 600 RR</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>R 352,900</t>
+          <t>R 58,900</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>10,966 km</t>
+          <t>32,466 km</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>George (WC)</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/22E612470</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/6B9613820</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1179,132 +1133,178 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:35:59</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>webuycars_22E612470</t>
+          <t>webuycars_6B9613820</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400 (3 listings)</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2008 Honda CBR 1000 RR Fireblade</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>R 80,900</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>34,461 km</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Germiston (GP)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/895302815</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 10:59:58</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_895302815</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+          <t>2009 Honda CB 600 Hornet</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>R 109,995</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+          <t>R 39,900</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>200km</t>
+          <t>68,126 km</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/824812136</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:21</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012465812701010354228509</t>
+          <t>webuycars_824812136</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Zzr 400 kawasaki</t>
+          <t>2009 Honda CBR 1000 RR Fireblade</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>R 7,500</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>123,456km</t>
+          <t>74,208 km</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Kroonstad</t>
+          <t>Silver Lakes (GP)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kroonstad/zzr-400-kawasaki/10013493850161013085967409</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/9E0302015</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:24</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013493850161013085967409</t>
+          <t>webuycars_9E0302015</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1314,502 +1314,640 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2019 Kawasaki Ninja 650 (ex650) ABS</t>
+          <t>2024 Honda CBR 1000rr-R</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R 72,900</t>
+          <t>R 352,900</t>
         </is>
       </c>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>19,765 km</t>
+          <t>10,966 km</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>George (WC)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/67E900160</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/22E612470</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:19</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>webuycars_67E900160</t>
+          <t>webuycars_22E612470</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>suzuki Gixxer 250 (3 listings)</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026 Honda NX 500</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>R131,990</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-honda-nx-500/</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 10:59:58</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-honda-nx-500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2024 Suzuki Gixxer 250 Cc (2nd Owner Since New)</t>
+          <t>2023 Honda CB 500X</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>R 42,500</t>
+          <t>R99,990</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>4,200km</t>
+          <t>10,571km</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Johannesburg South</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/2024-suzuki-gixxer-250-cc-2nd-owner-since-new/10013496103141012587794309</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-honda-cb-500x-2/</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:36</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013496103141012587794309</t>
+          <t>zabikers_2023-honda-cb-500x-2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Gixxer Naked 250fi</t>
+          <t>2025 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>R 45,000</t>
+          <t>R114,990</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>3,500km</t>
+          <t>744km</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Muizenberg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/muizenberg/suzuki-gixxer-naked-250fi/10013392378371010784220709</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-honda-cb-500-x-2/</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:37</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013392378371010784220709</t>
+          <t>zabikers_2025-honda-cb-500-x-2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2023 Suzuki 250 DS 250</t>
+          <t>2026 Honda NX 500</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>R 51,900</t>
+          <t>R131,990</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>15,999 km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/910309679</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-honda-nx-500/</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:35</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>webuycars_910309679</t>
+          <t>zabikers_2025-honda-nx-500</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 400 x (1 listings)</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2008 Honda CBR 1000RR Fireblade</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>R119,990</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>26,126km</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2008-honda-cbr-1000rr-fireblade-2/</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 10:59:58</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2008-honda-cbr-1000rr-fireblade-2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2019 Triumph Scrambler Street Scrambler</t>
+          <t>2012 Honda CBR 1000RR FIREBLADE ABS</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>R 91,900</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n"/>
+          <t>R129,990</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>16,469 km</t>
+          <t>48,351km</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2012-honda-cbr-1000rr-fireblade-abs/</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 400 x</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:36:50</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>webuycars_97BD12912</t>
+          <t>zabikers_2012-honda-cbr-1000rr-fireblade-abs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900 (2 listings)</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2013 Honda CBF 1000</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>R79,990</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>45,104km</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2013-honda-cbf-1000-2/</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500 X</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 10:59:58</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2013-honda-cbf-1000-2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Triumph speed twin 900</t>
+          <t>2006 Honda CBR 600RR Movistar Telefonica</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>R 24,900</t>
+          <t>R89,990</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>1,000km</t>
+          <t>37,934km</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2006-honda-cbr-600rr-movistar-telefonica/</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:13</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013424411931010005469309</t>
+          <t>zabikers_2006-honda-cbr-600rr-movistar-telefonica</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2019 Triumph Scrambler Street Scrambler</t>
+          <t>1984 Honda CB 1100 R</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>R 91,900</t>
+          <t>R283,990</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>16,469 km</t>
+          <t>555km</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/1984-honda-cb-1100-r/</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Triumph Scrambler 900</t>
+          <t>Honda CB 500 X</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:08</t>
+          <t>22-02-2026 10:59:58</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>webuycars_97BD12912</t>
+          <t>zabikers_1984-honda-cb-1100-r</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Triumph Speed 400 (3 listings)</t>
+          <t>Kawasaki Ninja 400 (6 listings)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2009 Triumph Speedmaster 865 Speedmaster EFI</t>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>R 42,900</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n"/>
+          <t>R 109,995</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>43,839 km</t>
+          <t>200km</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Pinetown</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/103713851</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:23</t>
+          <t>22-02-2026 11:00:20</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>webuycars_103713851</t>
+          <t>gumtree_10012465812701010354228509</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2015 Triumph Speedmaster 865 Speedmaster EFI</t>
+          <t>Zzr 400 kawasaki</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>R 40,900</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
+          <t>R 7,500</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>50,543 km</t>
+          <t>123,456km</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>Kroonstad</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/AA5A00028</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kroonstad/zzr-400-kawasaki/10013493850161013085967409</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:23</t>
+          <t>22-02-2026 11:00:24</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>webuycars_AA5A00028</t>
+          <t>gumtree_10013493850161013085967409</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1819,897 +1957,7045 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2022 Triumph Speed Triple RS</t>
+          <t>2019 Kawasaki Ninja 650 (ex650) ABS</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>R 171,900</t>
+          <t>R 72,900</t>
         </is>
       </c>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>17,155 km</t>
+          <t>19,765 km</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/E05B01946</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/67E900160</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Triumph Speed 400</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:23</t>
+          <t>22-02-2026 11:00:19</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>webuycars_E05B01946</t>
+          <t>webuycars_67E900160</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Ducati Scrambler (3 listings)</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2018 Kawasaki Ninja 400 ABS SE</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>R87,995</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>39,108km</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Twist Of The Wrist Motorcycles</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2018-kawasaki-ninja-400-abs-se/</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:19</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2018-kawasaki-ninja-400-abs-se</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2015 Ducati X Scrambler @Bike Bros Motorcycles!</t>
+          <t>2025 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>R 124,500</t>
+          <t>R124,900</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>11,349km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Retreat</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/retreat/2015-ducati-x-scrambler-64-bike-bros-motorcycles/10012503439581011067160209</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500-2/</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:58</t>
+          <t>22-02-2026 11:00:19</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012503439581011067160209</t>
+          <t>zabikers_2025-kawasaki-ninja-500-2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler 800 Urban Enduro 2015</t>
+          <t>2025 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>R 124,000</t>
+          <t>R124,990</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>11,100km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/other/ducati-scrambler-800-urban-enduro-2015/10013434253351010003065109</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500/</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Ducati Scrambler</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:37:58</t>
+          <t>22-02-2026 11:00:19</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013434253351010003065109</t>
+          <t>zabikers_2025-kawasaki-ninja-500</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Ducati Scrambler</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>2015 Ducati Scrambler Icon RED</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>R 54,900</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>55,001 km</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Midstream (GP)</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Ducati/Scrambler/7C2A03344</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>Ducati Scrambler</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>20-02-2026 10:37:56</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_7C2A03344</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250 (3 listings)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Yamaha MT 07 (1 listings)</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki Gixxer Naked 250fi</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>R 45,000</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>3,500km</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Muizenberg</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/muizenberg/suzuki-gixxer-naked-250fi/10013392378371010784220709</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:37</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013392378371010784220709</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>suzuki Gixxer 250</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>2025 Yamaha MT07 - MT 07 NEW</t>
+          <t>2023 Suzuki 250 DS 250</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>R 179,950</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
+          <t>R 51,900</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>15,999 km</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Kraaifontein</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kraaifontein/2025-yamaha-mt07-+-mt-07-new/10013416804491010004286409</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/910309679</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT 07</t>
+          <t>suzuki Gixxer 250</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:03</t>
+          <t>22-02-2026 11:00:34</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013416804491010004286409</t>
+          <t>webuycars_910309679</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>BMW G 310 (5 listings)</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>1992 Suzuki RGV 250</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>R99,990</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>30,201km</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/1992-suzuki-rgv-250/</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:34</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_1992-suzuki-rgv-250</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>BMW G310R 2022</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>R 55,000</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>5,740km</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Chatsworth</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/chatsworth/bmw-g310r-2022/10013491315601011124314909</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>BMW G 310</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>20-02-2026 10:38:23</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013491315601011124314909</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x (14 listings)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2020 BMW G310R</t>
+          <t>2019 Triumph Scrambler Street Scrambler</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>R 54,000</t>
+          <t>R 91,900</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>20,404km</t>
+          <t>16,469 km</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Strand</t>
+          <t>East London (EC)</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/strand/2020-bmw-g310r/10013500017401010054138109</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:23</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013500017401010054138109</t>
+          <t>webuycars_97BD12912</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>2015 BMW G Series G650 GS ABS H/grips</t>
+          <t>2026 Triumph Speed 400 400</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>R 65,900</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n"/>
+          <t>R93,000</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>33,076 km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Brackenfell (WC)</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/866314815</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400-2/</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:17</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>webuycars_866314815</t>
+          <t>zabikers_2026-triumph-speed-400-400-2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2008 BMW G Series G450 X</t>
+          <t>2026 Triumph Speed 400 400</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>R 29,900</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n"/>
+          <t>R93,000</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>8,076 km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Montana (GP)</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/76DE04781</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400/</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:17</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>webuycars_76DE04781</t>
+          <t>zabikers_2026-triumph-speed-400-400</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2014 BMW G Series G 650 GS Sertao ABS H/grips</t>
+          <t>2026 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>R 24,900</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n"/>
+          <t>R103,000</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>73,328 km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>George (WC)</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/CAF414786</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>BMW G 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:17</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>webuycars_CAF414786</t>
+          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>BMW GS 310 (1 listings)</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-4/</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:51</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2019 BMW R 310 GS 5015km only</t>
+          <t>2025 Triumph Speed 400 400</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>R 62,000</t>
+          <t>R89,900</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>5,015km</t>
+          <t>1,100km</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Langebaan</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/langebaan/2019-bmw-r-310-gs-5015km-only/10013489014211010017154009</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-400-400-3/</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>BMW GS 310</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:35</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013489014211010017154009</t>
+          <t>zabikers_2025-triumph-speed-400-400-3</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Z 400 (4 listings)</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed 400 400</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>R89,900</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-400-400-2/</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:51</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-400-400-2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Zzr 400 kawasaki</t>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>R 7,500</t>
+          <t>R99,900</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>123,456km</t>
+          <t>400km</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Kroonstad</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kroonstad/zzr-400-kawasaki/10013493850161013085967409</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:54</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013493850161013085967409</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>R 109,995</t>
+          <t>R99,900</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>200km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x/</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:54</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012465812701010354228509</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2007 Kawasaki ZX 14</t>
+          <t>2025 Triumph Scrambler 400 X</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>R 71,900</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>43,595 km</t>
+          <t>2,850km</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/F5BC02354</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z 400</t>
+          <t>Triumph Scrambler 400 x</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>20-02-2026 10:38:49</t>
+          <t>22-02-2026 11:00:51</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>webuycars_F5BC02354</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>3,900km</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:51</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2024 Triumph SPEED 400</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>R89,990</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>3,052km</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-400/</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:51</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2024-triumph-speed-400</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2012 Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>R89,990</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>28,461km</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2012-triumph-scrambler-900/</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:51</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2012-triumph-scrambler-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>R225,000</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>4,200km</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe/</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400 x</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:00:51</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-triumph-scrambler-1200-xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900 (15 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Triumph speed twin 900</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>R 24,900</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>1,000km</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:14</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013424411931010005469309</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>2019 Triumph Scrambler Street Scrambler</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>R 91,900</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>16,469 km</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>East London (EC)</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Scrambler/97BD12912</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_97BD12912</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2012 Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>R89,990</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>28,461km</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2012-triumph-scrambler-900/</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2012-triumph-scrambler-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2016 Triumph STREET TWIN 900</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>R99,990</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>10,230km</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2016-triumph-street-twin-900/</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2016-triumph-street-twin-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>2015 Triumph Thruxton 900</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>R89,990</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>7,516km</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2015-triumph-thruxton-900/</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2015-triumph-thruxton-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed Twin 900</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>R149,000</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>4,100km</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900/</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-twin-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>R225,000</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>4,200km</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe/</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-triumph-scrambler-1200-xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2026 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>R103,000</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-4/</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>400km</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x/</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>2,850km</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>3,900km</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph 900 Rally Pro</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>R249,990</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>6,173km</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-900-rally-pro/</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-900-rally-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed Twin 900 900</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>R159,000</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>2,900km</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900-900/</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:10</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-twin-900-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400 (23 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>2009 Triumph Speedmaster 865 Speedmaster EFI</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>R 42,900</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>43,839 km</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/103713851</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_103713851</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>2015 Triumph Speedmaster 865 Speedmaster EFI</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>R 40,900</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>50,543 km</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Richmond (WC)</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speedmaster/AA5A00028</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_AA5A00028</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>2022 Triumph Speed Triple RS</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>R 171,900</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>17,155 km</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/E05B01946</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_E05B01946</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>2026 Triumph Speed 400 400</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>R93,000</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400-2/</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-triumph-speed-400-400-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>2026 Triumph Speed 400 400</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>R93,000</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400/</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-triumph-speed-400-400</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>2026 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>R103,000</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-4/</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed 400 400</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>R89,900</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>1,100km</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-400-400-3/</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-400-400-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed 400 400</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>R89,900</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-400-400-2/</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-400-400-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>400km</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>100km</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x/</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>2,850km</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Scrambler 400 X</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>3,900km</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-scrambler-400-x</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>2024 Triumph SPEED 400</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>R89,990</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>3,052km</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-400/</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2024-triumph-speed-400</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>2017 Triumph Speed Triple 1050 S</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>R119,990</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>51,472km</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-triumph-speed-triple-1050-s/</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2017-triumph-speed-triple-1050-s</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>2021 Triumph SPEED TWIN 1200</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>R129,990</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>9,607km</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2021-triumph-speed-twin-1200/</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2021-triumph-speed-twin-1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>2026 Triumph Speed Twin 1200 1200</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>R229,000</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>900km</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-twin-1200-1200/</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-triumph-speed-twin-1200-1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>2013 Triumph Speed Triple R 1050 ABS</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>R127,995</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>32,557km</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Twist Of The Wrist Motorcycles</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2013-triumph-speed-triple-r-1050-abs/</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2013-triumph-speed-triple-r-1050-abs</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed Twin 900 900</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>R159,000</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>2,900km</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900-900/</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-twin-900-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed Triple 1200 RS Triple 1200 RS</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>R299,000</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>3,700km</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-triple-1200-rs-triple-1200-rs-2/</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-triple-1200-rs-triple-1200-rs-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed Triple 1200 RS Triple 1200 RS</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>R289,000</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>4,800km</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-triple-1200-rs-triple-1200-rs/</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-triple-1200-rs-triple-1200-rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>2025 Triumph Speed Twin 900</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>R149,000</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>4,100km</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900/</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-triumph-speed-twin-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>2024 Triumph Speed Triple 1200 RS</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>R229,000</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>6,500km</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-triple-1200-rs/</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Speed 400</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2024-triumph-speed-triple-1200-rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>yamaha xsr 700 (1 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>yamaha xsr 700</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha XSR900 GP</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>R269,950</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Linex Lynnwood</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/yamaha-xsr900-gp/</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>yamaha xsr 700</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:42</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_yamaha-xsr900-gp</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler (3 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2015 Ducati X Scrambler @Bike Bros Motorcycles!</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>R 124,500</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>11,349km</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Retreat</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/retreat/2015-ducati-x-scrambler-64-bike-bros-motorcycles/10012503439581011067160209</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:59</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10012503439581011067160209</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler 800 Urban Enduro 2015</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>R 124,000</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>11,100km</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/other/ducati-scrambler-800-urban-enduro-2015/10013434253351010003065109</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:59</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013434253351010003065109</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>2015 Ducati Scrambler Icon RED</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>R 54,900</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>55,001 km</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Ducati/Scrambler/7C2A03344</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:01:58</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_7C2A03344</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07 (7 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>2023 Yamaha MT-09 SP</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>R199,990</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>20,102km</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-yamaha-mt-09-sp/</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-yamaha-mt-09-sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>2015 Yamaha MT-09 TRACER</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>R119,990</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>23,917km</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2015-yamaha-mt-09-tracer-2/</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2015-yamaha-mt-09-tracer-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>2019 Yamaha MT-09</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>R159,990</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>9,661km</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2019-yamaha-mt-09/</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2019-yamaha-mt-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>2016 Yamaha MT-09 TRACER</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>R139,990</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>26,992km</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2016-yamaha-mt-09-tracer/</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2016-yamaha-mt-09-tracer</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>2017 Yamaha MT 09</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>R129,990</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>34,225km</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-yamaha-mt-09/</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2017-yamaha-mt-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>2015 Yamaha MT-09</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>R119,990</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>25,049km</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2015-yamaha-mt-09/</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2015-yamaha-mt-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT-09 Y-AMT version</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>R259,950</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Linex Sandton</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/yamaha-mt-09-y-amt-version/</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT 07</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:04</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_yamaha-mt-09-y-amt-version</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>BMW G 310 (10 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>2020 BMW G310R</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>R 54,000</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>20,404km</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Strand</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/strand/2020-bmw-g310r/10013500017401010054138109</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:25</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013500017401010054138109</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>BMW G310R 2022</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>R 55,000</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>5,740km</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Chatsworth</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/chatsworth/bmw-g310r-2022/10013491315601011124314909</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:25</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013491315601011124314909</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>2015 BMW G Series G650 GS ABS H/grips</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>R 65,900</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>33,076 km</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Brackenfell (WC)</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/866314815</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_866314815</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>2008 BMW G Series G450 X</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>R 29,900</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>8,076 km</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Montana (GP)</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/76DE04781</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_76DE04781</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>2014 BMW G Series G 650 GS Sertao ABS H/grips</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>R 24,900</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>73,328 km</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>George (WC)</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/BMW/G Series/CAF414786</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_CAF414786</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>2022 BMW G 310 GS</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>R69,000</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>9,930km</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>BMW Motorrad Centurion</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g-310-gs/</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2022-bmw-g-310-gs</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>2023 BMW G310 R</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>746km</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-r/</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-bmw-g310-r</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>2022 BMW G 310 GS</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>R85,995</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>6,501km</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Twist Of The Wrist Motorcycles</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g310-gs/</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2022-bmw-g310-gs</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>2016 BMW G650 GS</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>47,060km</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2016-bmw-g650-gs/</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2016-bmw-g650-gs</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>2023 BMW G310 GS TRIPLE BLACK</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>2,904km</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-gs-triple-black/</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>BMW G 310</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:19</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-bmw-g310-gs-triple-black</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>BMW GS 310 (4 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>2019 BMW R 310 GS 5015km only</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>R 62,000</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>5,015km</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Langebaan</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/langebaan/2019-bmw-r-310-gs-5015km-only/10013489014211010017154009</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:37</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013489014211010017154009</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>2022 BMW G 310 GS</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>R69,000</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>9,930km</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>BMW Motorrad Centurion</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g-310-gs/</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:35</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2022-bmw-g-310-gs</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>2022 BMW G 310 GS</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>R85,995</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>6,501km</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Twist Of The Wrist Motorcycles</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g310-gs/</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:35</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2022-bmw-g310-gs</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>2023 BMW G310 R</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>746km</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-r/</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>BMW GS 310</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:35</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-bmw-g310-r</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400 (20 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
           <t>Kawasaki Z 400</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Zzr 400 kawasaki</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>R 7,500</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>123,456km</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Kroonstad</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/kroonstad/zzr-400-kawasaki/10013493850161013085967409</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:56</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013493850161013085967409</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>R 109,995</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>200km</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Pinetown</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:56</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10012465812701010354228509</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>2007 Kawasaki ZX 14</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>R 71,900</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>43,595 km</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>Richmond (WC)</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/F5BC02354</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_F5BC02354</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>2007 Kawasaki ZX 14</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>R 64,900</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="inlineStr">
         <is>
           <t>61,929 km</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>Brackenfell (WC)</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/ZX/D21303206</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>Kawasaki Z 400</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>20-02-2026 10:38:49</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
         <is>
           <t>webuycars_D21303206</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>2018 Kawasaki Ninja 400 ABS SE</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>R87,995</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>39,108km</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Twist Of The Wrist Motorcycles</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2018-kawasaki-ninja-400-abs-se/</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2018-kawasaki-ninja-400-abs-se</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>2026 Kawasaki Z900</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>R219,990</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-kawasaki-z900/</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-kawasaki-z900</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>2024 Kawasaki Z900</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>R179,990</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>536km</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-kawasaki-z900/</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2024-kawasaki-z900</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>2012 Kawasaki Z1000 SX</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>R109,990</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>13,045km</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2012-kawasaki-z1000-sx/</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2012-kawasaki-z1000-sx</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>2021 Kawasaki Z1000 SX</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>R149,990</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>32,849km</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2021-kawasaki-z1000-sx/</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2021-kawasaki-z1000-sx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>2020 Kawasaki Z1000 SX</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>R169,990</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>12,655km</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2020-kawasaki-z1000-sx-2/</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2020-kawasaki-z1000-sx-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>2020 Kawasaki Z1000 SX</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>R169,990</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>11,559km</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2020-kawasaki-z1000-sx/</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2020-kawasaki-z1000-sx</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>2016 Kawasaki Z1000</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>R159,990</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>5,720km</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2016-kawasaki-z1000/</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2016-kawasaki-z1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>2019 Kawasaki Z1000 Ohlins Edition</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>R169,990</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>40,985km</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2019-kawasaki-z1000-ohlins-edition/</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2019-kawasaki-z1000-ohlins-edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>1979 Kawasaki Z 750</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>83,612km</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/1979-kawasaki-z-750/</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_1979-kawasaki-z-750</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>2016 Kawasaki ZX-6R 636 ABS</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>R146,995</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>36,660km</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Twist Of The Wrist Motorcycles</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2016-kawasaki-zx-6r-636-abs/</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2016-kawasaki-zx-6r-636-abs</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>2025 Kawasaki Z650 RS</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>R139,990</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-z650-rs-3/</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-kawasaki-z650-rs-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>2025 Kawasaki Z900 ABS</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>R219,990</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-z900-abs/</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-kawasaki-z900-abs</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>2025 Kawasaki ZX-10R</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>R369,990</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-zx-10r/</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-kawasaki-zx-10r</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>2025 Kawasaki Z650 RS</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>R139,990</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-z650-rs-2/</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-kawasaki-z650-rs-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>2025 Kawasaki ZX 1100 SX</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>R299,990</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-zx-1100-sx/</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z 400</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:02:51</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-kawasaki-zx-1100-sx</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200 (24 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy Pacer 200 Pacer 200</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>R 24,900</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>24 km</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>East London (EC)</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Pacer 200/0F2A11517</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_0F2A11517</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy Pacer 200 Pacer 200</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>R 18,900</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>199 km</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>Gqeberha (EC)</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Pacer 200/CA1D07416</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_CA1D07416</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy CGL Cgl/ccl/velocity 150</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>R 15,900</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>42 km</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Pietermaritzburg (KZN)</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/18EC05125</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_18EC05125</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>2021 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>R 24,900</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>141 km</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>Germiston (GP)</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/9F6703932</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_9F6703932</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>2024 Big Boy Mustang 250</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>R 33,900</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>230 km</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>Montana (GP)</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Mustang/93F803700</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_93F803700</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>2026 Big Boy TSR  250</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>R 28,900</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>411 km</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>Witbank (MP)</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/09AD04154</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_09AD04154</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>2023 Big Boy Velocity Cargo 150</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>R 14,700</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>2,358 km</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>Lansdowne (WC)</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/10E214734</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_10E214734</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>2023 Big Boy Revival 150</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>R 14,400</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>1,887 km</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Revival/7D3E03305</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_7D3E03305</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>2024 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>R 24,900</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>2,356 km</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Gqeberha (EC)</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/938A01152</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_938A01152</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>2024 Big Boy TSR Superlight125</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>R 21,900</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>3,006 km</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/271C01004</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_271C01004</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>2021 Big Boy TSR 125</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>R 19,900</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>2,703 km</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Germiston (GP)</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/DAE903926</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_DAE903926</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>2026 Big Boy 125 DLite</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>R 14,400</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>2,903 km</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>Silver Lakes (GP)</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/125/F0E605551</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_F0E605551</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>2023 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>R 16,900</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>8,027 km</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>Mbombela (MP)</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/972708452</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_972708452</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>2023 Big Boy Velocity Cargo 150</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>R 13,900</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr"/>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>5,891 km</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>Pietermaritzburg (KZN)</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/E91F09443</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_E91F09443</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>2024 Big Boy CGL Cgl/ccl/velocity 150</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>R 12,900</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>9,417 km</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>Rustenburg (NW)</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/9F2B16907</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_9F2B16907</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>2021 Big Boy Velocity Cargo 150</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>R 12,900</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr"/>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/F31D04500</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_F31D04500</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>2023 Big Boy CGL Cgl/ccl/velocity 150</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>R 13,400</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>21,742 km</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>Dome (GP)</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/AE4603069</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_AE4603069</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>2020 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>R 21,900</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr"/>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>21,836 km</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/BC0311542</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_BC0311542</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>2018 Big Boy Revival 150</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>R 12,900</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>1,124 km</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Montana (GP)</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Revival/E55417144</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_E55417144</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>2012 Big Boy Revival 150</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>R 10,900</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr"/>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>6,944 km</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>Silver Lakes (GP)</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Revival/B36104908</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_B36104908</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy CGL D-Lite 125</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>R 10,900</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr"/>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>10,725 km</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>Dome (GP)</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/DBCE14191</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_DBCE14191</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>2026 Big Boy Velocity Cargo 150</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr"/>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>457 km</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>Richmond (WC)</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/781407546</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_781407546</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy Velocity Cargo 150</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr"/>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>199 km</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>JHB South (GP)</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/873D06865</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_873D06865</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>2024 Big Boy Mustang 250</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr"/>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>12,851 km</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>Riverhorse (KZN)</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Mustang/940107366</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:07</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_940107366</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100 (2 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>2018 Triumph Bonneville Speedmaster</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>R119,000</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr"/>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>10,500km</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2018-triumph-bonneville-speedmaster/</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:22</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2018-triumph-bonneville-speedmaster</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>2021 Triumph Bonneville SPEED MASTER</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>R139,990</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>4,942km</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2021-triumph-bonneville-speed-master/</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2026 11:03:22</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2021-triumph-bonneville-speed-master</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>Total Listings:</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="B176" s="6" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>Bikes Tracked:</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="B177" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>Sources:</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="B178" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>Price Drops Detected:</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B179" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>Last Updated:</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>20/02/2026 10:39:12</t>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>22/02/2026 11:03:42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A39:K39"/>
+  <mergeCells count="17">
+    <mergeCell ref="A97:K97"/>
+    <mergeCell ref="A101:K101"/>
+    <mergeCell ref="A171:K171"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="A55:K55"/>
     <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A125:K125"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:29</t>
+          <t>31-03-2026 15:13:09</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:29</t>
+          <t>31-03-2026 15:13:09</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:29</t>
+          <t>31-03-2026 15:13:09</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:40</t>
+          <t>31-03-2026 15:13:17</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:38</t>
+          <t>31-03-2026 15:13:16</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:38</t>
+          <t>31-03-2026 15:13:16</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:38</t>
+          <t>31-03-2026 15:13:16</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:38</t>
+          <t>31-03-2026 15:13:16</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:51</t>
+          <t>31-03-2026 15:13:27</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:47</t>
+          <t>31-03-2026 15:13:24</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:55</t>
+          <t>31-03-2026 15:13:32</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:19:54</t>
+          <t>31-03-2026 15:13:31</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:05</t>
+          <t>31-03-2026 15:13:39</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:05</t>
+          <t>31-03-2026 15:13:39</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:07</t>
+          <t>31-03-2026 15:13:41</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:07</t>
+          <t>31-03-2026 15:13:41</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:07</t>
+          <t>31-03-2026 15:13:41</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:03</t>
+          <t>31-03-2026 15:13:38</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -3304,7 +3304,7 @@
           <t>R89,000</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>4,000km</t>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:12</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
@@ -3357,7 +3357,7 @@
           <t>R89,000</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>3,000km</t>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:12</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -3410,7 +3410,7 @@
           <t>R99,900</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>500km</t>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:12</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
@@ -3463,7 +3463,7 @@
           <t>R103,000</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>100km</t>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:12</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -3516,7 +3516,7 @@
           <t>R93,995</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>13,008km</t>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:12</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
@@ -3569,7 +3569,7 @@
           <t>R225,000</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>4,200km</t>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:13</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
           <t>R215,000</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>3,600km</t>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:13</t>
+          <t>31-03-2026 15:13:47</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:25</t>
+          <t>31-03-2026 15:13:56</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -3841,7 +3841,7 @@
           <t>R89,000</t>
         </is>
       </c>
-      <c r="E70" s="4" t="n"/>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>4,000km</t>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
           <t>R89,000</t>
         </is>
       </c>
-      <c r="E71" s="4" t="n"/>
+      <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>3,000km</t>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
@@ -3947,7 +3947,7 @@
           <t>R99,900</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n"/>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>500km</t>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
           <t>R103,000</t>
         </is>
       </c>
-      <c r="E73" s="4" t="n"/>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>100km</t>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
@@ -4053,7 +4053,7 @@
           <t>R225,000</t>
         </is>
       </c>
-      <c r="E74" s="4" t="n"/>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>4,200km</t>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
@@ -4106,7 +4106,7 @@
           <t>R215,000</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n"/>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>3,600km</t>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
@@ -4159,7 +4159,7 @@
           <t>R93,995</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n"/>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>13,008km</t>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:21</t>
+          <t>31-03-2026 15:13:52</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:29</t>
+          <t>31-03-2026 15:14:00</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:37</t>
+          <t>31-03-2026 15:14:08</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:37</t>
+          <t>31-03-2026 15:14:08</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:37</t>
+          <t>31-03-2026 15:14:08</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:45</t>
+          <t>31-03-2026 15:14:16</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:44</t>
+          <t>31-03-2026 15:14:15</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:44</t>
+          <t>31-03-2026 15:14:15</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:55</t>
+          <t>31-03-2026 15:14:26</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:00</t>
+          <t>31-03-2026 15:14:32</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
@@ -5943,7 +5943,7 @@
           <t>R69,990</t>
         </is>
       </c>
-      <c r="E114" s="4" t="n"/>
+      <c r="E114" s="4" t="inlineStr"/>
       <c r="F114" s="4" t="inlineStr">
         <is>
           <t>6,077km</t>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
@@ -6049,7 +6049,7 @@
           <t>R69,900</t>
         </is>
       </c>
-      <c r="E116" s="4" t="n"/>
+      <c r="E116" s="4" t="inlineStr"/>
       <c r="F116" s="4" t="inlineStr">
         <is>
           <t>80km</t>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
@@ -6261,7 +6261,7 @@
           <t>R69,990</t>
         </is>
       </c>
-      <c r="E120" s="4" t="n"/>
+      <c r="E120" s="4" t="inlineStr"/>
       <c r="F120" s="4" t="inlineStr">
         <is>
           <t>1,836km</t>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
           <t>R69,990</t>
         </is>
       </c>
-      <c r="E121" s="4" t="n"/>
+      <c r="E121" s="4" t="inlineStr"/>
       <c r="F121" s="4" t="inlineStr">
         <is>
           <t>746km</t>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:20:59</t>
+          <t>31-03-2026 15:14:31</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
@@ -6427,7 +6427,7 @@
           <t>R69,990</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="inlineStr">
         <is>
           <t>6,077km</t>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:03</t>
+          <t>31-03-2026 15:14:35</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
@@ -6480,7 +6480,7 @@
           <t>R69,900</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="inlineStr">
         <is>
           <t>80km</t>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:03</t>
+          <t>31-03-2026 15:14:35</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
@@ -6533,7 +6533,7 @@
           <t>R69,990</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
           <t>1,836km</t>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:03</t>
+          <t>31-03-2026 15:14:35</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
@@ -6586,7 +6586,7 @@
           <t>R69,990</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="n"/>
       <c r="F127" s="4" t="inlineStr">
         <is>
           <t>746km</t>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:03</t>
+          <t>31-03-2026 15:14:35</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:07</t>
+          <t>31-03-2026 15:14:40</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:12</t>
+          <t>31-03-2026 15:14:45</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:11</t>
+          <t>31-03-2026 15:14:44</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:20</t>
+          <t>31-03-2026 15:14:53</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:20</t>
+          <t>31-03-2026 15:14:53</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 12:21:20</t>
+          <t>31-03-2026 15:14:53</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026 12:21:32</t>
+          <t>31/03/2026 15:15:06</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00e44c65"/>
         <bgColor rgb="00e44c65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00c8e6c9"/>
+        <bgColor rgb="00c8e6c9"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,8 +104,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K178"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -541,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Suzuki V-STROM 250SX (3 listings)</t>
+          <t>Suzuki V-STROM 250SX (2 listings)</t>
         </is>
       </c>
     </row>
@@ -553,33 +565,33 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2023 Suzuki V-Strom 250 SX</t>
+          <t>2024 Suzuki DS 250 V-Strom SX</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>R 52,900</t>
+          <t>R54,990</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>6,766 km</t>
+          <t>1,855km</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Montana (GP)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/V-Strom/93DE10355</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-suzuki-ds-250-v-strom-sx-2/</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -589,12 +601,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:09</t>
+          <t>26-04-2026 08:50:08</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>webuycars_93DE10355</t>
+          <t>zabikers_2024-suzuki-ds-250-v-strom-sx-2</t>
         </is>
       </c>
     </row>
@@ -606,33 +618,33 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2023 Suzuki V-Strom 250 SX</t>
+          <t>2024 Suzuki DS 250 V-Strom SX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>R 49,900</t>
+          <t>R59,990</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>8,093 km</t>
+          <t>4,366km</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/V-Strom/9BC513981</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-suzuki-ds-250-v-strom-sx-3/</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -642,72 +654,72 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:09</t>
+          <t>26-04-2026 08:50:08</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9BC513981</t>
+          <t>zabikers_2024-suzuki-ds-250-v-strom-sx-3</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Suzuki V-STROM 250SX</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Lifan X Trail 250 (4 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Lifan X Trail 250</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ZABikers</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2024 Suzuki DS 250 V-Strom SX</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>R54,990</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1,855km</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026 Lifan X-Trail 250</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>R26,990</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1km</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Bikeshop Rivonia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-suzuki-ds-250-v-strom-sx-2/</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Suzuki V-STROM 250SX</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:09</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2024-suzuki-ds-250-v-strom-sx-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Lifan X Trail 250 (5 listings)</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-lifan-x-trail-250-2/</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Lifan X Trail 250</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:18</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2026-lifan-x-trail-250-2</t>
         </is>
       </c>
     </row>
@@ -719,33 +731,33 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Lifan 250cc</t>
+          <t>2025 Lifan X-Trail 250</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>R 25,000</t>
+          <t>R26,990</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>150km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Hillcrest</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/hillcrest/lifan-250cc/10013522262521010256810009</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-lifan-x-trail-250/</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -755,12 +767,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:17</t>
+          <t>26-04-2026 08:50:18</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013522262521010256810009</t>
+          <t>zabikers_2025-lifan-x-trail-250</t>
         </is>
       </c>
     </row>
@@ -777,7 +789,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2025 Lifan X-Trail 250</t>
+          <t>2026 Lifan X-Trail 250</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -788,7 +800,7 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>1km</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -798,7 +810,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-lifan-x-trail-250-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-lifan-x-trail-250/</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -808,12 +820,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:16</t>
+          <t>26-04-2026 08:50:18</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-lifan-x-trail-250-2</t>
+          <t>zabikers_2026-lifan-x-trail-250</t>
         </is>
       </c>
     </row>
@@ -851,7 +863,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-lifan-x-trail-250/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-lifan-x-trail-250-2/</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -861,125 +873,125 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:16</t>
+          <t>26-04-2026 08:50:18</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-lifan-x-trail-250</t>
+          <t>zabikers_2025-lifan-x-trail-250-2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Lifan X Trail 250</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>2026 Lifan X-Trail 250</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>R26,990</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1km</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-lifan-x-trail-250-2/</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Lifan X Trail 250</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:16</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2026-lifan-x-trail-250-2</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Honda CB 500X (23 listings)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Lifan X Trail 250</t>
+          <t>Honda CB 500X</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026 Lifan X-Trail 250</t>
+          <t>Honda XL 500s</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>R26,990</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
+          <t>R 15,000</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
+          <t>10,000km</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/other/honda-xl-500s/10013553547431013065001009</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500X</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:29</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013553547431013065001009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500X</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Honda NX500</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>R 131,399</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>1km</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-lifan-x-trail-250/</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Lifan X Trail 250</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:16</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2026-lifan-x-trail-250</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Honda CB 500X (18 listings)</t>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Pinetown</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500X</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:29</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>gumtree_10013320405561010354228509</t>
         </is>
       </c>
     </row>
@@ -991,33 +1003,33 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Honda NX500</t>
+          <t>2023 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>R 131,399</t>
+          <t>R 89,900</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1km</t>
+          <t>2,436 km</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/honda-nx500/10013320405561010354228509</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/2A1102636</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1027,12 +1039,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:27</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013320405561010354228509</t>
+          <t>webuycars_2A1102636</t>
         </is>
       </c>
     </row>
@@ -1054,23 +1066,23 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>R 70,900</t>
+          <t>R 78,900</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>13,270 km</t>
+          <t>7,905 km</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Riverhorse (KZN)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/D7A213344</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/138C01836</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1080,12 +1092,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>webuycars_D7A213344</t>
+          <t>webuycars_138C01836</t>
         </is>
       </c>
     </row>
@@ -1102,28 +1114,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2010 Honda CBR 1000 RR Fireblade</t>
+          <t>2023 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>R 89,900</t>
+          <t>R 66,900</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>34,223 km</t>
+          <t>13,270 km</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>East London (EC)</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/DDEB08933</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CB/D7A213344</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1133,12 +1145,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>webuycars_DDEB08933</t>
+          <t>webuycars_D7A213344</t>
         </is>
       </c>
     </row>
@@ -1155,28 +1167,28 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2006 Honda CBR 1000rr</t>
+          <t>2010 Honda CBR 1000 RR Fireblade</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>R 58,900</t>
+          <t>R 87,900</t>
         </is>
       </c>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>76,813 km</t>
+          <t>34,223 km</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/4C1510990</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/DDEB08933</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1186,12 +1198,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4C1510990</t>
+          <t>webuycars_DDEB08933</t>
         </is>
       </c>
     </row>
@@ -1208,28 +1220,28 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2007 Honda CBR 1000 RR Fireblade</t>
+          <t>2007 Honda CBR 1000rr</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>R 74,900</t>
+          <t>R 58,900</t>
         </is>
       </c>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>81,687 km</t>
+          <t>75,809 km</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Brackenfell (WC)</t>
+          <t>Silver Lakes (GP)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/B1C009096</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBR/D45202302</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1239,12 +1251,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>webuycars_B1C009096</t>
+          <t>webuycars_D45202302</t>
         </is>
       </c>
     </row>
@@ -1256,33 +1268,33 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2012 Honda CBF 600s</t>
+          <t>2025 Honda CB 500 X</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>R 25,900</t>
+          <t>R99,990</t>
         </is>
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>116,757 km</t>
+          <t>744km</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Honda/CBF/1A0508807</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-honda-cb-500-x-3/</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1292,12 +1304,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>webuycars_1A0508807</t>
+          <t>zabikers_2025-honda-cb-500-x-3</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1331,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>R99,990</t>
+          <t>R94,990</t>
         </is>
       </c>
       <c r="E19" s="4" t="n"/>
@@ -1335,7 +1347,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-honda-cb-500x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-honda-cb-500x-3/</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1345,12 +1357,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-honda-cb-500x-2</t>
+          <t>zabikers_2023-honda-cb-500x-3</t>
         </is>
       </c>
     </row>
@@ -1367,18 +1379,18 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2025 Honda CB 500 X</t>
+          <t>2023 Honda CB 500X</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>R109,990</t>
+          <t>R89,990</t>
         </is>
       </c>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>744km</t>
+          <t>13,379km</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1388,7 +1400,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-honda-cb-500-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-honda-cb-500x-4/</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1398,12 +1410,12 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-honda-cb-500-x-2</t>
+          <t>zabikers_2023-honda-cb-500x-4</t>
         </is>
       </c>
     </row>
@@ -1420,28 +1432,28 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2026 Honda CBR1000RR-R Fireblade SP</t>
+          <t>2009 Honda CBR 1000RR</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>R569,599</t>
+          <t>R119,900</t>
         </is>
       </c>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>49,813km</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-honda-cbr1000rr-r-fireblade-sp/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2009-honda-cbr-1000rr/</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1451,12 +1463,12 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-honda-cbr1000rr-r-fireblade-sp</t>
+          <t>zabikers_2009-honda-cbr-1000rr</t>
         </is>
       </c>
     </row>
@@ -1473,28 +1485,28 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>1980 Honda CB 750</t>
+          <t>2017 Honda CBR 1000RR</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>R85,990</t>
+          <t>R219,900</t>
         </is>
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>21,565km</t>
+          <t>17,971km</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/1980-honda-cb-750/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-honda-cbr-1000rr/</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1504,12 +1516,12 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>zabikers_1980-honda-cb-750</t>
+          <t>zabikers_2017-honda-cbr-1000rr</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1569,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1579,28 +1591,28 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>1984 Honda CB 1100 R</t>
+          <t>2008 Honda CBR 1000R</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>R283,990</t>
+          <t>R89,900</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>555km</t>
+          <t>32,100km</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/1984-honda-cb-1100-r/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2008-honda-cbr-1000r/</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1610,12 +1622,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>zabikers_1984-honda-cb-1100-r</t>
+          <t>zabikers_2008-honda-cbr-1000r</t>
         </is>
       </c>
     </row>
@@ -1632,28 +1644,28 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2012 Honda CBR 1000 RR</t>
+          <t>2012 Honda CBR 1000RR</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>R119,900</t>
+          <t>R134,900</t>
         </is>
       </c>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>61,021km</t>
+          <t>30,918km</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2012-honda-cbr-1000-rr/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2012-honda-cbr-1000rr/</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1663,12 +1675,12 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2012-honda-cbr-1000-rr</t>
+          <t>zabikers_2012-honda-cbr-1000rr</t>
         </is>
       </c>
     </row>
@@ -1685,28 +1697,28 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2026 Honda CB 1000 SP HONET</t>
+          <t>2008 Honda CBR 1000RR</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>R229,950</t>
+          <t>R119,900</t>
         </is>
       </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>39,800km</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Gold Rand</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-honda-cb-1000-sp-honet/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2008-honda-cbr-1000rr/</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1716,12 +1728,12 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-honda-cb-1000-sp-honet</t>
+          <t>zabikers_2008-honda-cbr-1000rr</t>
         </is>
       </c>
     </row>
@@ -1738,18 +1750,18 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2010 Honda CBR 1000RR Fireblade Carbon ABS</t>
+          <t>2026 Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>R139,990</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
+          <t>R569,599</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>22,426km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1759,7 +1771,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2010-honda-cbr-1000rr-fireblade-carbon-abs/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-honda-cbr1000rr-r-fireblade-sp-2/</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1769,12 +1781,12 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2010-honda-cbr-1000rr-fireblade-carbon-abs</t>
+          <t>zabikers_2026-honda-cbr1000rr-r-fireblade-sp-2</t>
         </is>
       </c>
     </row>
@@ -1791,28 +1803,28 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2008 Honda CBR 1000R</t>
+          <t>2026 Honda CB 1000 SP HONET</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>R89,900</t>
+          <t>R229,950</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>32,100km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>TRD Motorcycles</t>
+          <t>Harley-Davidson Gold Rand</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2008-honda-cbr-1000r/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-honda-cb-1000-sp-honet/</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1822,12 +1834,12 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2008-honda-cbr-1000r</t>
+          <t>zabikers_2026-honda-cb-1000-sp-honet</t>
         </is>
       </c>
     </row>
@@ -1844,28 +1856,28 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2012 Honda CBR 1000RR</t>
+          <t>2021 Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>R134,900</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
+          <t>R349,990</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>30,918km</t>
+          <t>8,573km</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>TRD Motorcycles</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2012-honda-cbr-1000rr/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2021-honda-cbr1000rr-r-fireblade-sp/</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1875,12 +1887,12 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:24</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2012-honda-cbr-1000rr</t>
+          <t>zabikers_2021-honda-cbr1000rr-r-fireblade-sp</t>
         </is>
       </c>
     </row>
@@ -1897,209 +1909,209 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2017 Honda CBR 1000RR</t>
+          <t>1984 Honda CB 1100 R</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>R219,900</t>
+          <t>R283,990</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>17,971km</t>
+          <t>555km</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/1984-honda-cb-1100-r/</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500X</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:26</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_1984-honda-cb-1100-r</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB 500X</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2015 Honda CBR 1000rr (abs)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>R159,900</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>29,375km</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
           <t>TRD Motorcycles</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2017-honda-cbr-1000rr/</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2015-honda-cbr-1000rr-abs/</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Honda CB 500X</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:24</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2017-honda-cbr-1000rr</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400 (10 listings)</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:26</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2015-honda-cbr-1000rr-abs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500X</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
+          <t>2012 Honda CBR 600 RR (Abs)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>R 109,995</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n"/>
+          <t>R99,950</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>200km</t>
+          <t>27,794km</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Pinetown</t>
+          <t>Harley-Davidson Gold Rand</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2012-honda-cbr-600-rr-abs/</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500X</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:32</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10012465812701010354228509</t>
+          <t>zabikers_2012-honda-cbr-600-rr-abs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500X</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2023 Kawasaki Ninja 400 ABS (ex400g)</t>
+          <t>2017 Honda CBR 1000RR</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>R 88,900</t>
+          <t>R179,900</t>
         </is>
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>9,351 km</t>
+          <t>37,437km</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/D27C03223</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-honda-cbr-1000rr-2/</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja 400</t>
+          <t>Honda CB 500X</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:31</t>
+          <t>26-04-2026 08:50:26</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>webuycars_D27C03223</t>
+          <t>zabikers_2017-honda-cbr-1000rr-2</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>2025 Kawasaki Ninja 500</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>R 92,900</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>1,529 km</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Vereeniging (GP)</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/816113216</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Kawasaki Ninja 400</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:31</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_816113216</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400 (11 listings)</t>
         </is>
       </c>
     </row>
@@ -2111,33 +2123,33 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>2025 Kawasaki Ninja 500</t>
+          <t>2023 Kawasaki Ninja 400 SE ABS Demo</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>R 105,900</t>
+          <t>R 109,995</t>
         </is>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>623 km</t>
+          <t>200km</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Riverhorse (KZN)</t>
+          <t>Pinetown</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/2B7804407</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pinetown/2023-kawasaki-ninja-400-se-abs-demo/10012465812701010354228509</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2147,12 +2159,12 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:31</t>
+          <t>26-04-2026 08:50:35</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>webuycars_2B7804407</t>
+          <t>gumtree_10012465812701010354228509</t>
         </is>
       </c>
     </row>
@@ -2164,33 +2176,33 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2019 Kawasaki Z 400</t>
+          <t>Kawasaki Ninja 400cc - Limited edition</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>R79,990</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
+          <t>R 147,900</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>23,164km</t>
+          <t>47km</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2019-kawasaki-z-400/</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/richards-bay/kawasaki-ninja-400cc-+-limited-edition/10013538153241012842217209</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2200,12 +2212,12 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:31</t>
+          <t>26-04-2026 08:50:36</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2019-kawasaki-z-400</t>
+          <t>gumtree_10013538153241012842217209</t>
         </is>
       </c>
     </row>
@@ -2217,33 +2229,33 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2025 Kawasaki Ninja 500</t>
+          <t>2019 Kawasaki Ninja 400 ABS SE (ex400g)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>R124,900</t>
+          <t>R 68,000</t>
         </is>
       </c>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>2,372 km</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Polokwane (L)</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500-2/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/860205550</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2253,65 +2265,69 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:31</t>
+          <t>26-04-2026 08:50:32</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-kawasaki-ninja-500-2</t>
+          <t>webuycars_860205550</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Kawasaki Ninja 400</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>2025 Kawasaki Ninja 500</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>R124,990</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>0km</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500/</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>R 96,900</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>R 100,900</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>623 km</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Riverhorse (KZN)</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/2B7804407</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Kawasaki Ninja 400</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:31</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2025-kawasaki-ninja-500</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:32</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_2B7804407</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2339,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2333,23 +2349,23 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>R124,990</t>
+          <t>R 104,900</t>
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>1km</t>
+          <t>3,363 km</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Montana (GP)</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-kawasaki-ninja-500-2/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Kawasaki/Ninja/85BC06567</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2359,12 +2375,12 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:31</t>
+          <t>26-04-2026 08:50:32</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-kawasaki-ninja-500-2</t>
+          <t>webuycars_85BC06567</t>
         </is>
       </c>
     </row>
@@ -2381,18 +2397,18 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2026 Kawasaki Ninja 500</t>
+          <t>2025 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>R124,990</t>
+          <t>R119,990</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>1km</t>
+          <t>3,225km</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2402,7 +2418,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-kawasaki-ninja-500/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500-4/</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2412,12 +2428,12 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:31</t>
+          <t>26-04-2026 08:50:32</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-kawasaki-ninja-500</t>
+          <t>zabikers_2025-kawasaki-ninja-500-4</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2450,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2025 Kawasaki Ninja ZX-10R</t>
+          <t>2025 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>R369,995</t>
+          <t>R124,990</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
@@ -2450,246 +2466,246 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500/</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:32</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-kawasaki-ninja-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Ninja 400</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2025 Kawasaki Ninja ZX-10R</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>R369,995</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>0km</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
           <t>Linex Lynnwood</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-zx-10r/</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>Kawasaki Ninja 400</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:31</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:32</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>zabikers_2025-kawasaki-ninja-zx-10r</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>suzuki Gixxer 250 (15 listings)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2022 Suzuki Gixxer 250cc Abs ( Well Maintained)</t>
+          <t>2025 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>R 36,000</t>
+          <t>R124,900</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>8,000km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Johannesburg South</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/2022-suzuki-gixxer-250cc-abs-well-maintained/10013533070481012782117709</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-kawasaki-ninja-500-2/</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:39</t>
+          <t>26-04-2026 08:50:32</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013533070481012782117709</t>
+          <t>zabikers_2025-kawasaki-ninja-500-2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Gixxer 250 Cc (excellent Condition)</t>
+          <t>2026 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>R 37,800</t>
+          <t>R124,990</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>12,000km</t>
+          <t>1km</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Johannesburg South</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/suzuki-gixxer-250-cc-excellent-condition/10013525984931012587794309</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-kawasaki-ninja-500-2/</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:39</t>
+          <t>26-04-2026 08:50:32</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013525984931012587794309</t>
+          <t>zabikers_2026-kawasaki-ninja-500-2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>2023 suzuki Gixxer SF250</t>
+          <t>2026 Kawasaki Ninja 500</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>R 45,999</t>
+          <t>R124,990</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>33,000km</t>
+          <t>1km</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>East London</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/east-london/2023-suzuki-gixxer-sf250/10013533235911010041956109</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-kawasaki-ninja-500/</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>suzuki Gixxer 250</t>
+          <t>Kawasaki Ninja 400</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:41</t>
+          <t>26-04-2026 08:50:32</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013533235911010041956109</t>
+          <t>zabikers_2026-kawasaki-ninja-500</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>suzuki Gixxer 250</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>2023 Suzuki Gixxer 250SF</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>R 45,000</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>11,000km</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Pietermaritzburg</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/pietermaritzburg/2023-suzuki-gixxer-250sf/10013531915641010338128109</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>suzuki Gixxer 250</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:41</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013531915641010338128109</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250 (12 listings)</t>
         </is>
       </c>
     </row>
@@ -2706,28 +2722,28 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Gixxer Naked 250fi</t>
+          <t>2023 Suzuki Gixxer 250cc (as New)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>R 50,000</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n"/>
+          <t>R 42,000</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>4,000km</t>
+          <t>16,000km</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Muizenberg</t>
+          <t>Johannesburg South</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/muizenberg/suzuki-gixxer-naked-250fi/10013392378371010784220709</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/2023-suzuki-gixxer-250cc-as-new/10013553519631012487665009</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -2737,12 +2753,12 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:41</t>
+          <t>26-04-2026 08:50:42</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013392378371010784220709</t>
+          <t>gumtree_10013553519631012487665009</t>
         </is>
       </c>
     </row>
@@ -2754,33 +2770,33 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2025 Suzuki 250 DS 250</t>
+          <t>Suzuki Gixxer 250 Cc (excellent Condition)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>R 52,900</t>
+          <t>R 34,000</t>
         </is>
       </c>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2,827 km</t>
+          <t>12,000km</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Montana (GP)</t>
+          <t>Johannesburg South</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/69F514238</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/suzuki-gixxer-250-cc-excellent-condition/10013548790141012587794309</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -2790,65 +2806,69 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:42</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>webuycars_69F514238</t>
+          <t>gumtree_10013548790141012587794309</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>suzuki Gixxer 250</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>2025 Suzuki 250 DS 250</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>R 49,900</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>801 km</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Polokwane (L)</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/7C7D16660</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Gumtree</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>2023 suzuki Gixxer SF250</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>R 42,000</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>R 45,999</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>33,000km</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>East London</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/east-london/2023-suzuki-gixxer-sf250/10013533235911010041956109</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>suzuki Gixxer 250</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:38</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_7C7D16660</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:43</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>gumtree_10013533235911010041956109</t>
         </is>
       </c>
     </row>
@@ -2860,33 +2880,33 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2023 Suzuki 250 DS 250</t>
+          <t>Suzuki RM 250</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>R 47,900</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
+          <t>R 27,000</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>4,412 km</t>
+          <t>123km</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Pietermaritzburg (KZN)</t>
+          <t>Eastern Pretoria</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/C59F08120</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/eastern-pretoria/suzuki-rm-250/10013552825541010941848009</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -2896,12 +2916,12 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:44</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>webuycars_C59F08120</t>
+          <t>gumtree_10013552825541010941848009</t>
         </is>
       </c>
     </row>
@@ -2918,28 +2938,28 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>2025 Suzuki 250 DS 250</t>
+          <t>2026 Suzuki 250 DS 250</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>R 54,900</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n"/>
+          <t>R 57,900</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>5,871 km</t>
+          <t>153 km</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>George (WC)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/856508115</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Suzuki/250/868908687</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -2949,12 +2969,12 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>webuycars_856508115</t>
+          <t>webuycars_868908687</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2996,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>R55,900</t>
+          <t>R62,500</t>
         </is>
       </c>
       <c r="E52" s="4" t="n"/>
@@ -2992,7 +3012,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-f-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-f/</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3002,12 +3022,12 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-suzuki-gsx-250-f-2</t>
+          <t>zabikers_2026-suzuki-gsx-250-f</t>
         </is>
       </c>
     </row>
@@ -3024,28 +3044,28 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>2026 Suzuki GSX 250 FR</t>
+          <t>2024 Suzuki DS 250</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>R61,950</t>
+          <t>R49,900</t>
         </is>
       </c>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>13,762km</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-fr/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-suzuki-ds-250/</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3055,12 +3075,12 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-suzuki-gsx-250-fr</t>
+          <t>zabikers_2024-suzuki-ds-250</t>
         </is>
       </c>
     </row>
@@ -3077,18 +3097,18 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>2024 Suzuki GSX 250 F</t>
+          <t>2026 Suzuki GSX 250 N</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>R54,900</t>
+          <t>R55,250</t>
         </is>
       </c>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2,500km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3098,7 +3118,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-suzuki-gsx-250-f/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-n/</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3108,12 +3128,12 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-suzuki-gsx-250-f</t>
+          <t>zabikers_2026-suzuki-gsx-250-n</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3150,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>2026 Suzuki GSX 250 N</t>
+          <t>2026 Suzuki GSX 250 F</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>R55,250</t>
+          <t>R62,900</t>
         </is>
       </c>
       <c r="E55" s="4" t="n"/>
@@ -3151,7 +3171,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-n/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-f-3/</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3161,12 +3181,12 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-suzuki-gsx-250-n</t>
+          <t>zabikers_2026-suzuki-gsx-250-f-3</t>
         </is>
       </c>
     </row>
@@ -3183,28 +3203,28 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>2026 Suzuki GSX 250 F</t>
+          <t>2022 Suzuki GIXXER 250</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>R61,950</t>
+          <t>R49,900</t>
         </is>
       </c>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>12,000km</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-f/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-suzuki-gixxer-250/</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3214,12 +3234,12 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-suzuki-gsx-250-f</t>
+          <t>zabikers_2022-suzuki-gixxer-250</t>
         </is>
       </c>
     </row>
@@ -3236,28 +3256,28 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>1992 Suzuki RGV 250</t>
+          <t>2026 Suzuki GSX 250 F</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>R99,990</t>
+          <t>R55,900</t>
         </is>
       </c>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>30,201km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Bikeshop Boksburg</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/1992-suzuki-rgv-250/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-suzuki-gsx-250-f-2/</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3267,72 +3287,72 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:38</t>
+          <t>26-04-2026 08:50:41</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>zabikers_1992-suzuki-rgv-250</t>
+          <t>zabikers_2026-suzuki-gsx-250-f-2</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2025 Suzuki DS 250 V Strom</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>R49,900</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>2,631km</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Boksburg</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-suzuki-ds-250-v-strom/</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>suzuki Gixxer 250</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:41</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2025-suzuki-ds-250-v-strom</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Triumph Scrambler 400x (7 listings)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 400x</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>2025 Triumph Scrambler 400 X</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>R89,000</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>4,000km</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Johannesburg</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 400x</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:47</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2025-triumph-scrambler-400-x</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3400,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:47</t>
+          <t>26-04-2026 08:50:47</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -3402,28 +3422,28 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Scrambler 400 X 400 X</t>
+          <t>2024 Triumph Scrambler 400X</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>R99,900</t>
+          <t>R93,995</t>
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>500km</t>
+          <t>13,008km</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Twist Of The Wrist Motorcycles</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400x/</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3433,12 +3453,12 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:47</t>
+          <t>26-04-2026 08:50:47</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
+          <t>zabikers_2024-triumph-scrambler-400x</t>
         </is>
       </c>
     </row>
@@ -3455,18 +3475,18 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>2026 Triumph Scrambler 400 X 400 X</t>
+          <t>2024 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>R103,000</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n"/>
+          <t>R69,000</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>100km</t>
+          <t>15,500km</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -3476,7 +3496,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3486,12 +3506,12 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:47</t>
+          <t>26-04-2026 08:50:47</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
+          <t>zabikers_2024-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -3508,28 +3528,28 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>2024 Triumph Scrambler 400X</t>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>R93,995</t>
+          <t>R99,900</t>
         </is>
       </c>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>13,008km</t>
+          <t>500km</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Twist Of The Wrist Motorcycles</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400x/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3539,12 +3559,12 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:47</t>
+          <t>26-04-2026 08:50:47</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-triumph-scrambler-400x</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -3561,18 +3581,18 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+          <t>2026 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>R225,000</t>
+          <t>R103,000</t>
         </is>
       </c>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>4,200km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3582,7 +3602,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3592,12 +3612,12 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:47</t>
+          <t>26-04-2026 08:50:47</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-triumph-scrambler-1200-xe</t>
+          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -3614,18 +3634,18 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+          <t>2025 Triumph Scrambler 400 X</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>R215,000</t>
+          <t>R89,000</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>3,600km</t>
+          <t>4,000km</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3635,7 +3655,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3645,72 +3665,72 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:47</t>
+          <t>26-04-2026 08:50:47</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-triumph-scrambler-1200-xe-2</t>
+          <t>zabikers_2025-triumph-scrambler-400-x</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900 (12 listings)</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400x</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>R225,000</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>4,200km</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Johannesburg</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe/</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 400x</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:50:47</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2023-triumph-scrambler-1200-xe</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Triumph speed twin 900</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>R 24,900</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>1,000km</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>George</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/george/triumph-speed-twin-900/10013424411931010005469309</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Scrambler 900</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:13:56</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013424411931010005469309</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Scrambler 900 (11 listings)</t>
         </is>
       </c>
     </row>
@@ -3722,33 +3742,33 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>Gumtree</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>2015 Triumph Thruxton 900</t>
+          <t>2015 Triumph Scrambler 900</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>R89,990</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="n"/>
+          <t>R 79,000</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>7,516km</t>
+          <t>12,406km</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Port Elizabeth</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2015-triumph-thruxton-900/</t>
+          <t>https://www.gumtree.co.za/a-motorcycles-scooters/port-elizabeth/2015-triumph-scrambler-900/10013550588261010850284509</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3758,12 +3778,12 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:58</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2015-triumph-thruxton-900</t>
+          <t>gumtree_10013550588261010850284509</t>
         </is>
       </c>
     </row>
@@ -3780,28 +3800,28 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Speed Twin 900</t>
+          <t>2015 Triumph Thruxton 900</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>R149,000</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n"/>
+          <t>R84,990</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>4,200km</t>
+          <t>7,516km</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2015-triumph-thruxton-900-2/</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3811,12 +3831,12 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-speed-twin-900</t>
+          <t>zabikers_2015-triumph-thruxton-900-2</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3864,7 @@
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>4,000km</t>
+          <t>3,000km</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -3854,7 +3874,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -3864,12 +3884,12 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
         </is>
       </c>
     </row>
@@ -3886,28 +3906,28 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Scrambler 400 X</t>
+          <t>2024 Triumph Scrambler 400X</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>R89,000</t>
+          <t>R93,995</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>3,000km</t>
+          <t>13,008km</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Twist Of The Wrist Motorcycles</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400x/</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -3917,12 +3937,12 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
+          <t>zabikers_2024-triumph-scrambler-400x</t>
         </is>
       </c>
     </row>
@@ -3939,18 +3959,18 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Scrambler 400 X 400 X</t>
+          <t>2024 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>R99,900</t>
+          <t>R69,000</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>500km</t>
+          <t>15,500km</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -3960,7 +3980,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -3970,12 +3990,12 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
+          <t>zabikers_2024-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -3992,18 +4012,18 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>2026 Triumph Scrambler 400 X 400 X</t>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>R103,000</t>
+          <t>R99,900</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>100km</t>
+          <t>500km</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4013,7 +4033,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4023,12 +4043,12 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -4045,18 +4065,18 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+          <t>2026 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>R225,000</t>
+          <t>R103,000</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>4,200km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -4066,7 +4086,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4076,12 +4096,12 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-triumph-scrambler-1200-xe</t>
+          <t>zabikers_2026-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -4098,18 +4118,18 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>2023 Triumph SCRAMBLER 1200 XE</t>
+          <t>2025 Triumph Scrambler 400 X</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>R215,000</t>
+          <t>R89,000</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>3,600km</t>
+          <t>4,000km</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4119,7 +4139,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4129,12 +4149,12 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-triumph-scrambler-1200-xe-2</t>
+          <t>zabikers_2025-triumph-scrambler-400-x</t>
         </is>
       </c>
     </row>
@@ -4151,28 +4171,28 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>2024 Triumph Scrambler 400X</t>
+          <t>2023 Triumph SCRAMBLER 1200 XE</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>R93,995</t>
+          <t>R225,000</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>13,008km</t>
+          <t>4,200km</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Twist Of The Wrist Motorcycles</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400x/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-triumph-scrambler-1200-xe/</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4182,12 +4202,12 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-triumph-scrambler-400x</t>
+          <t>zabikers_2023-triumph-scrambler-1200-xe</t>
         </is>
       </c>
     </row>
@@ -4204,28 +4224,28 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph 900 Rally Pro</t>
+          <t>2025 Triumph Speed Twin 900 900</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>R249,990</t>
+          <t>R159,000</t>
         </is>
       </c>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>6,173km</t>
+          <t>4,200km</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-900-rally-pro/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900-900/</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4235,12 +4255,12 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-900-rally-pro</t>
+          <t>zabikers_2025-triumph-speed-twin-900-900</t>
         </is>
       </c>
     </row>
@@ -4257,28 +4277,28 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Speed Twin 900 900</t>
+          <t>2025 Triumph 900 Rally Pro</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>R159,000</t>
+          <t>R239,990</t>
         </is>
       </c>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>3,700km</t>
+          <t>6,173km</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900-900/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-900-rally-pro/</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4288,12 +4308,12 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:13:52</t>
+          <t>26-04-2026 08:50:57</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-speed-twin-900-900</t>
+          <t>zabikers_2025-triumph-900-rally-pro</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4342,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>R 79,900</t>
+          <t>R 75,900</t>
         </is>
       </c>
       <c r="E80" s="4" t="n"/>
@@ -4348,7 +4368,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -4358,53 +4378,57 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Triumph Speed 400</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>2013 Triumph Speed Triple 1050</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>R 57,900</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>R 51,900</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>R 54,900</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>81,679 km</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Richmond (WC)</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>https://www.webuycars.co.za/buy-a-car/Triumph/Speed Triple/921008836</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Triumph Speed 400</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:00</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:51:04</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>webuycars_921008836</t>
         </is>
@@ -4423,28 +4447,28 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>2024 Triumph SPEED 400</t>
+          <t>2025 Triumph Speed 400 400</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>R89,990</t>
+          <t>R89,900</t>
         </is>
       </c>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>3,052km</t>
+          <t>2,300km</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-400/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-400-400-3/</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4454,12 +4478,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-triumph-speed-400</t>
+          <t>zabikers_2025-triumph-speed-400-400-3</t>
         </is>
       </c>
     </row>
@@ -4476,28 +4500,28 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>2024 Triumph Speed 400 X</t>
+          <t>2026 Triumph Speed 400 400</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>R79,900</t>
+          <t>R93,000</t>
         </is>
       </c>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>9,952km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-400-x/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400-2/</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4507,12 +4531,12 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-triumph-speed-400-x</t>
+          <t>zabikers_2026-triumph-speed-400-400-2</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4564,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>4,000km</t>
+          <t>3,000km</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4550,7 +4574,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4560,12 +4584,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
         </is>
       </c>
     </row>
@@ -4582,28 +4606,28 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Scrambler 400 X</t>
+          <t>2024 Triumph SPEED 400</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>R89,000</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr"/>
+          <t>R84,990</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>3,000km</t>
+          <t>3,052km</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-400-2/</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4613,12 +4637,12 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x-2</t>
+          <t>zabikers_2024-triumph-speed-400-2</t>
         </is>
       </c>
     </row>
@@ -4635,18 +4659,18 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Scrambler 400 X 400 X</t>
+          <t>2024 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>R99,900</t>
+          <t>R69,000</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>500km</t>
+          <t>15,500km</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -4656,7 +4680,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4666,12 +4690,12 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
+          <t>zabikers_2024-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4743,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
@@ -4741,18 +4765,18 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Speed 400 400</t>
+          <t>2025 Triumph Scrambler 400 X 400 X</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>R89,900</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="n"/>
+          <t>R99,900</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>1,800km</t>
+          <t>500km</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -4762,7 +4786,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-400-400-3/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x-400-x-2/</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -4772,12 +4796,12 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-speed-400-400-3</t>
+          <t>zabikers_2025-triumph-scrambler-400-x-400-x-2</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4849,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
@@ -4847,28 +4871,28 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>2026 Triumph Speed 400 400</t>
+          <t>2024 Triumph Speed 400 X</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>R93,000</t>
+          <t>R79,900</t>
         </is>
       </c>
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>100km</t>
+          <t>9,952km</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Bikeshop Boksburg</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-triumph-speed-400-x/</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -4878,12 +4902,12 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-triumph-speed-400-400</t>
+          <t>zabikers_2024-triumph-speed-400-x</t>
         </is>
       </c>
     </row>
@@ -4900,18 +4924,18 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>2026 Triumph Speed 400 400</t>
+          <t>2025 Triumph Scrambler 400 X</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>R93,000</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="n"/>
+          <t>R89,000</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>100km</t>
+          <t>4,000km</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -4921,7 +4945,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-scrambler-400-x/</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -4931,12 +4955,12 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-triumph-speed-400-400-2</t>
+          <t>zabikers_2025-triumph-scrambler-400-x</t>
         </is>
       </c>
     </row>
@@ -4953,28 +4977,28 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>2017 Triumph Speed Triple 1050 S</t>
+          <t>2026 Triumph Speed 400 400</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>R119,990</t>
+          <t>R93,000</t>
         </is>
       </c>
       <c r="E92" s="4" t="n"/>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>51,472km</t>
+          <t>100km</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2017-triumph-speed-triple-1050-s/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-400-400/</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -4984,12 +5008,12 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2017-triumph-speed-triple-1050-s</t>
+          <t>zabikers_2026-triumph-speed-400-400</t>
         </is>
       </c>
     </row>
@@ -5006,28 +5030,28 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>2021 Triumph SPEED TWIN 1200</t>
+          <t>2026 Triumph Speed Twin 1200 1200</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>R129,990</t>
+          <t>R229,000</t>
         </is>
       </c>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>9,607km</t>
+          <t>3,600km</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2021-triumph-speed-twin-1200/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-twin-1200-1200/</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -5037,12 +5061,12 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2021-triumph-speed-twin-1200</t>
+          <t>zabikers_2026-triumph-speed-twin-1200-1200</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5114,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -5112,28 +5136,28 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Speed Twin 900</t>
+          <t>2022 Triumph Speed Triple 1200 RS</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>R149,000</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
+          <t>R219,900</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>4,200km</t>
+          <t>28,500km</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-twin-900/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-triumph-speed-triple-1200-rs/</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -5143,12 +5167,12 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-speed-twin-900</t>
+          <t>zabikers_2022-triumph-speed-triple-1200-rs</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5200,7 @@
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>4,800km</t>
+          <t>5,000km</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -5196,7 +5220,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
@@ -5218,28 +5242,28 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>2025 Triumph Speed Triple 1200 RS Triple 1200 RS</t>
+          <t>2022 Triumph SPEED TRIPLE RS 1200</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>R299,000</t>
+          <t>R219,900</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>3,700km</t>
+          <t>28,500km</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>TRD Motorcycles</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-triple-1200-rs-triple-1200-rs-2/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-triumph-speed-triple-rs-1200/</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -5249,12 +5273,12 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-triumph-speed-triple-1200-rs-triple-1200-rs-2</t>
+          <t>zabikers_2022-triumph-speed-triple-rs-1200</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5306,7 @@
       <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>3,700km</t>
+          <t>4,200km</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -5302,7 +5326,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
@@ -5324,28 +5348,28 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>2026 Triumph Speed Twin 1200 1200</t>
+          <t>2017 Triumph Speed Triple 1050 S</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>R229,000</t>
+          <t>R119,990</t>
         </is>
       </c>
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2,600km</t>
+          <t>51,472km</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2026-triumph-speed-twin-1200-1200/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-triumph-speed-triple-1050-s/</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -5355,12 +5379,12 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2026-triumph-speed-twin-1200-1200</t>
+          <t>zabikers_2017-triumph-speed-triple-1050-s</t>
         </is>
       </c>
     </row>
@@ -5377,28 +5401,28 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>2022 Triumph SPEED TRIPLE RS 1200</t>
+          <t>2013 Triumph Speed Triple R 1050 ABS</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>R219,900</t>
+          <t>R127,995</t>
         </is>
       </c>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>28,500km</t>
+          <t>32,557km</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>TRD Motorcycles</t>
+          <t>Twist Of The Wrist Motorcycles</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2022-triumph-speed-triple-rs-1200/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2013-triumph-speed-triple-r-1050-abs/</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -5408,12 +5432,12 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2022-triumph-speed-triple-rs-1200</t>
+          <t>zabikers_2013-triumph-speed-triple-r-1050-abs</t>
         </is>
       </c>
     </row>
@@ -5430,28 +5454,28 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>2013 Triumph Speed Triple R 1050 ABS</t>
+          <t>2025 Triumph Speed Triple 1200 RS Triple 1200 RS</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>R127,995</t>
+          <t>R299,000</t>
         </is>
       </c>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>32,557km</t>
+          <t>3,800km</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Twist Of The Wrist Motorcycles</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2013-triumph-speed-triple-r-1050-abs/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2025-triumph-speed-triple-1200-rs-triple-1200-rs-2/</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -5461,12 +5485,12 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:00</t>
+          <t>26-04-2026 08:51:04</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2013-triumph-speed-triple-r-1050-abs</t>
+          <t>zabikers_2025-triumph-speed-triple-1200-rs-triple-1200-rs-2</t>
         </is>
       </c>
     </row>
@@ -5490,28 +5514,28 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>2024 Yamaha XSR 900</t>
+          <t>2017 Yamaha XSR 900</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>R179,990</t>
+          <t>R139,900</t>
         </is>
       </c>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>2,870km</t>
+          <t>40,320km</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Bikeshop Boksburg</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-yamaha-xsr-900/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-yamaha-xsr-900/</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -5521,12 +5545,12 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:08</t>
+          <t>26-04-2026 08:51:19</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-yamaha-xsr-900</t>
+          <t>zabikers_2017-yamaha-xsr-900</t>
         </is>
       </c>
     </row>
@@ -5543,28 +5567,28 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>2017 Yamaha XSR 900</t>
+          <t>Yamaha XSR900 GP</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>R139,900</t>
+          <t>R269,950</t>
         </is>
       </c>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>40,320km</t>
+          <t>0km</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>Linex Lynnwood</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2017-yamaha-xsr-900/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/yamaha-xsr900-gp/</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -5574,12 +5598,12 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:08</t>
+          <t>26-04-2026 08:51:19</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2017-yamaha-xsr-900</t>
+          <t>zabikers_yamaha-xsr900-gp</t>
         </is>
       </c>
     </row>
@@ -5596,28 +5620,28 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Yamaha XSR900 GP</t>
+          <t>2024 Yamaha XSR 900</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>R269,950</t>
+          <t>R179,990</t>
         </is>
       </c>
       <c r="E105" s="4" t="n"/>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>0km</t>
+          <t>2,870km</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Linex Lynnwood</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/yamaha-xsr900-gp/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-yamaha-xsr-900/</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -5627,19 +5651,19 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:08</t>
+          <t>26-04-2026 08:51:19</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>zabikers_yamaha-xsr900-gp</t>
+          <t>zabikers_2024-yamaha-xsr-900</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Ducati Scrambler (3 listings)</t>
+          <t>Ducati Scrambler (4 listings)</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5711,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:16</t>
+          <t>26-04-2026 08:51:27</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -5697,55 +5721,59 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>Ducati Scrambler</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>2018 Ducati Scrambler Cafe Racer</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>R 99,900</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>6,164 km</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>Riverhorse (KZN)</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Ducati/Scrambler/AFD714047</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>2016 Ducati Scrambler Icon RED</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>R 94,900</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>R 98,900</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>17,377 km</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Midstream (GP)</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Ducati/Scrambler/4F2115540</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Ducati Scrambler</t>
         </is>
       </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:15</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_AFD714047</t>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:51:26</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_4F2115540</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5821,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:15</t>
+          <t>26-04-2026 08:51:26</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -5803,69 +5831,115 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Yamaha MT07 (1 listings)</t>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>ZABikers</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>2015 Ducati Scrambler FULL THROTTLE 800</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>R119,900</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>11,109km</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Boksburg</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2015-ducati-scrambler-full-throttle-800/</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>Ducati Scrambler</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:51:26</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2015-ducati-scrambler-full-throttle-800</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>Yamaha MT07</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>BMW G310 (3 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>BMW G310</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>ZABikers</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>2020 Yamaha MT-07</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>R118,995</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>25,080km</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>Twist Of The Wrist Motorcycles</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2020-yamaha-mt-07/</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>Yamaha MT07</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:26</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2020-yamaha-mt-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>BMW G310 (10 listings)</t>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>2022 BMW G310 R</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>6,077km</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Bikeshop Rivonia</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g310-r-3/</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>BMW G310</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:51:45</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>zabikers_2022-bmw-g310-r-3</t>
         </is>
       </c>
     </row>
@@ -5877,33 +5951,33 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Gumtree</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Bmw G310 Abs  In Excellent Condition</t>
+          <t>2023 BMW G310 GS</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>R 39,500</t>
+          <t>R79,900</t>
         </is>
       </c>
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>25,000km</t>
+          <t>18,306km</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>Johannesburg South</t>
+          <t>Bikeshop Boksburg</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/johannesburg-south/bmw-g310-abs-in-excellent-condition/10013530329631013028420809</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-gs/</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -5913,12 +5987,12 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:32</t>
+          <t>26-04-2026 08:51:45</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>gumtree_10013530329631013028420809</t>
+          <t>zabikers_2023-bmw-g310-gs</t>
         </is>
       </c>
     </row>
@@ -5935,28 +6009,28 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>2022 BMW G310 R</t>
+          <t>2024 BMW G310 GS Style Triple Black</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>R69,990</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr"/>
+          <t>R79,900</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>6,077km</t>
+          <t>2,000km</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Triumph Johannesburg</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g310-r-3/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2024-bmw-g310-gs-style-triple-black/</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -5966,72 +6040,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:51:45</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2022-bmw-g310-r-3</t>
+          <t>zabikers_2024-bmw-g310-gs-style-triple-black</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>BMW G310</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>2023 BMW G310 GS TRIPLE BLACK</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>R69,990</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>2,904km</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-gs-triple-black/</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
-        <is>
-          <t>BMW G310</t>
-        </is>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:31</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2023-bmw-g310-gs-triple-black</t>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>BMW GS310 (1 listings)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>BMW GS310</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -6041,700 +6069,808 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>2025 BMW G310R</t>
+          <t>2022 BMW G310 R</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>R69,900</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr"/>
+          <t>R69,990</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>80km</t>
+          <t>6,077km</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-bmw-g310r/</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g310-r-3/</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>BMW GS310</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:51:51</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-bmw-g310r</t>
+          <t>zabikers_2022-bmw-g310-r-3</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>BMW G310</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>2018 BMW G310 GS</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>R59,900</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>4,696km</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Boksburg</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2018-bmw-g310-gs-3/</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>BMW G310</t>
-        </is>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:31</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2018-bmw-g310-gs-3</t>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200 (38 listings)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>2018 BMW G310 GS</t>
+          <t>2024 Big Boy Pacer 200 Pacer 200</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>R69,900</t>
+          <t>R 14,900</t>
         </is>
       </c>
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>17,145km</t>
+          <t>9,046 km</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>Brackenfell (WC)</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2018-bmw-g310-gs-2/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Pacer 200/4DED08387</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2018-bmw-g310-gs-2</t>
+          <t>webuycars_4DED08387</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>2023 BMW G310 GS</t>
+          <t>2026 Big Boy CGL D-Lite 125</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>R79,900</t>
+          <t>R 16,700</t>
         </is>
       </c>
       <c r="E119" s="4" t="n"/>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>18,306km</t>
+          <t>11 km</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>Polokwane (L)</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-gs/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/246106482</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-bmw-g310-gs</t>
+          <t>webuycars_246106482</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>2023 BMW G310 R</t>
+          <t>2021 Big Boy Revival RCT 150</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>R69,990</t>
+          <t>R 13,900</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr"/>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>1,836km</t>
+          <t>108 km</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Polokwane (L)</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-r-2/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Revival/566307901</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-bmw-g310-r-2</t>
+          <t>webuycars_566307901</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>2023 BMW G310 R</t>
+          <t>2024 Big Boy Mustang 250</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>R69,990</t>
+          <t>R 24,900</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>746km</t>
+          <t>165 km</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Springfield (KZN)</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-r/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Mustang/E69C10112</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2023-bmw-g310-r</t>
+          <t>webuycars_E69C10112</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>2024 BMW G310 GS Style Triple Black</t>
+          <t>2025 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>R79,900</t>
+          <t>R 15,900</t>
         </is>
       </c>
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>2,000km</t>
+          <t>669 km</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Triumph Johannesburg</t>
+          <t>Mbombela (MP)</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2024-bmw-g310-gs-style-triple-black/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/024D04358</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>BMW G310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:31</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2024-bmw-g310-gs-style-triple-black</t>
+          <t>webuycars_024D04358</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>BMW GS310 (4 listings)</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy Mustang 250</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>R 26,400</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>836 km</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>East London (EC)</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Mustang/5D7F01740</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_5D7F01740</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>BMW GS310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>2022 BMW G310 R</t>
+          <t>2024 Big Boy Zooka RFZ 125t</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>R69,990</t>
+          <t>R 11,900</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>6,077km</t>
+          <t>1,001 km</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2022-bmw-g310-r-3/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Zooka/220506649</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>BMW GS310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:35</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2022-bmw-g310-r-3</t>
+          <t>webuycars_220506649</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>BMW GS310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>2025 BMW G310R</t>
+          <t>2022 Big Boy Zooka RFZ 125j</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>R69,900</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="n"/>
+          <t>R 9,400</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr"/>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>80km</t>
+          <t>1,001 km</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Boksburg</t>
+          <t>Brackenfell (WC)</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2025-bmw-g310r/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Zooka/791808235</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>BMW GS310</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:35</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2025-bmw-g310r</t>
+          <t>webuycars_791808235</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>BMW GS310</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>2023 BMW G310 R</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>R69,990</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>1,836km</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-r-2/</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>BMW GS310</t>
-        </is>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:35</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2023-bmw-g310-r-2</t>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>2025 Big Boy Adventure 150</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>R 16,900</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>R 18,900</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>1,603 km</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>George (WC)</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Adventure/A41315109</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_A41315109</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>BMW GS310</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>2023 BMW G310 R</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>R69,990</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>746km</t>
-        </is>
-      </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2023-bmw-g310-r/</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>BMW GS310</t>
-        </is>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:35</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2023-bmw-g310-r</t>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>2024 Big Boy 125 Legend 125</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>R 15,900</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>R 17,900</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>1,319 km</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>George (WC)</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/125/E3E506218</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_E3E506218</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Kawasaki Z400 (1 listings)</t>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>2023 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>R 20,900</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>R 22,900</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>2,135 km</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Dome (GP)</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/A5E812682</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_A5E812682</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z400</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>ZABikers</t>
+          <t>WeBuyCars</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>2019 Kawasaki Z 400</t>
+          <t>2025 Big Boy Velocity Cargo 200</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>R79,990</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="n"/>
+          <t>R 18,900</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr"/>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>23,164km</t>
+          <t>2,552 km</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Bikeshop Rivonia</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2019-kawasaki-z-400/</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/0E9510499</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z400</t>
+          <t>Big Boy Pacer 200</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:40</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>zabikers_2019-kawasaki-z-400</t>
+          <t>webuycars_0E9510499</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200 (37 listings)</t>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>2025 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>R 25,700</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>2,989 km</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Riverhorse (KZN)</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/3EB308003</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_3EB308003</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Gumtree</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>2022 Big Boy 200 Velocity</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>R 12,000</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="n"/>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>14,389km</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>Randburg</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gumtree.co.za/a-motorcycles-scooters/randburg/2022-big-boy-200-velocity/10013532815381010032944709</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>2024 Big Boy Superlight 125</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>R 16,400</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>R 18,400</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>3,666 km</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>Brackenfell (WC)</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Superlight/D64A00628</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:45</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>gumtree_10013532815381010032944709</t>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_D64A00628</t>
         </is>
       </c>
     </row>
@@ -6751,28 +6887,28 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy Pacer 200 Pacer 200</t>
+          <t>2025 Big Boy CGL Cgl/ccl/velocity 150</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>R 18,900</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="n"/>
+          <t>R 15,900</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr"/>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>24 km</t>
+          <t>4,289 km</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Pacer 200/0F2A11517</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/042C09036</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -6782,12 +6918,12 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>webuycars_0F2A11517</t>
+          <t>webuycars_042C09036</t>
         </is>
       </c>
     </row>
@@ -6804,28 +6940,28 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>2024 Big Boy Pacer 200 Pacer 200</t>
+          <t>2025 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>R 17,900</t>
+          <t>R 15,900</t>
         </is>
       </c>
       <c r="E133" s="4" t="n"/>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>9,046 km</t>
+          <t>4,460 km</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Brackenfell (WC)</t>
+          <t>East London (EC)</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Pacer 200/4DED08387</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/1E3603749</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -6835,12 +6971,12 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>webuycars_4DED08387</t>
+          <t>webuycars_1E3603749</t>
         </is>
       </c>
     </row>
@@ -6857,96 +6993,100 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
+          <t>2018 Big Boy CGL Cgl/ccl/velocity 200</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>R 15,900</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>5,438 km</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Pietermaritzburg (KZN)</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/0F2209146</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>webuycars_0F2209146</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Big Boy Pacer 200</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>WeBuyCars</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
           <t>2025 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>R 15,900</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>1,360 km</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>Silver Lakes (GP)</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/A83005987</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>R 11,900</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>R 12,900</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>5,061 km</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>Lansdowne (WC)</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/3DE315811</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_A83005987</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>2021 Big Boy Adventure 150</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>R 14,900</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>3,417 km</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>Dome (GP)</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Adventure/7EF314137</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_7EF314137</t>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_3DE315811</t>
         </is>
       </c>
     </row>
@@ -6963,28 +7103,28 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy TSR 250</t>
+          <t>2024 Big Boy TSR 125</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>R 24,900</t>
+          <t>R 22,900</t>
         </is>
       </c>
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>4,088 km</t>
+          <t>5,763 km</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Brackenfell (WC)</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/6C8414265</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/76A206325</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -6994,65 +7134,69 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>webuycars_6C8414265</t>
+          <t>webuycars_76A206325</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="A137" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>2026 Big Boy TSR  250</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>R 28,900</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>411 km</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>Witbank (MP)</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/09AD04154</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>2025 Big Boy Revival 150</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>R 14,900</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>R 16,900</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>6,140 km</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Richmond (WC)</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Revival/BCDD15680</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_09AD04154</t>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_BCDD15680</t>
         </is>
       </c>
     </row>
@@ -7069,28 +7213,28 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>2026 Big Boy Velocity Cargo 150</t>
+          <t>2026 Big Boy Mustang 250</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>R 16,900</t>
+          <t>R 32,900</t>
         </is>
       </c>
       <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>523 km</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>Polokwane (L)</t>
+          <t>George (WC)</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/27E308064</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Mustang/A9D802658</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -7100,12 +7244,12 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>webuycars_27E308064</t>
+          <t>webuycars_A9D802658</t>
         </is>
       </c>
     </row>
@@ -7122,28 +7266,28 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy Mustang 250</t>
+          <t>2024 Big Boy D Lite 125</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>R 28,400</t>
+          <t>R 14,900</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>836 km</t>
+          <t>9,809 km</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Montana (GP)</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Mustang/5D7F01740</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/D Lite/5ADB07374</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -7153,12 +7297,12 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>webuycars_5D7F01740</t>
+          <t>webuycars_5ADB07374</t>
         </is>
       </c>
     </row>
@@ -7175,28 +7319,28 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>2026 Big Boy CGL Cgl/ccl/velocity 200</t>
+          <t>2023 Big Boy CGL Cgl/ccl/velocity 150</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>R 17,900</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="n"/>
+          <t>R 13,900</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr"/>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>636 km</t>
+          <t>9,343 km</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Witbank (MP)</t>
+          <t>Germiston (GP)</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/6CDB01809</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/940610004</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -7206,12 +7350,12 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>webuycars_6CDB01809</t>
+          <t>webuycars_940610004</t>
         </is>
       </c>
     </row>
@@ -7228,28 +7372,28 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy D Lite 125</t>
+          <t>2020 Big Boy CGL Cgl/ccl/velocity 150</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>R 14,900</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="n"/>
+          <t>R 13,400</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr"/>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>1,032 km</t>
+          <t>9,368 km</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Germiston (GP)</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/D Lite/148E06971</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/F8B409648</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -7259,12 +7403,12 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>webuycars_148E06971</t>
+          <t>webuycars_F8B409648</t>
         </is>
       </c>
     </row>
@@ -7281,28 +7425,28 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>2024 Big Boy TTX 125S</t>
+          <t>2025 Big Boy Adventure 150</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>R 12,900</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="n"/>
+          <t>R 14,900</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr"/>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>1,001 km</t>
+          <t>12,452 km</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Riverhorse (KZN)</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TTX/220506649</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Adventure/3C4911174</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -7312,12 +7456,12 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>webuycars_220506649</t>
+          <t>webuycars_3C4911174</t>
         </is>
       </c>
     </row>
@@ -7334,28 +7478,28 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy CGL Cgl/ccl/velocity 200</t>
+          <t>2024 Big Boy D Lite 125</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>R 19,900</t>
+          <t>R 11,900</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>1,964 km</t>
+          <t>16,964 km</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Germiston (GP)</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/3C8B11988</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/D Lite/04DA01184</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -7365,12 +7509,12 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>webuycars_3C8B11988</t>
+          <t>webuycars_04DA01184</t>
         </is>
       </c>
     </row>
@@ -7387,28 +7531,28 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy Velocity Cargo 150</t>
+          <t>2024 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>R 14,900</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="n"/>
+          <t>R 13,900</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr"/>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>1,802 km</t>
+          <t>17,857 km</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>Riverhorse (KZN)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/54F007731</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/E51108131</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -7418,118 +7562,126 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>webuycars_54F007731</t>
+          <t>webuycars_E51108131</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>2024 Big Boy 125 Legend 125</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>R 19,900</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>1,319 km</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>George (WC)</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/125/E3E506218</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>2024 Big Boy Velocity Cargo 150</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>R 11,900</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>R 12,900</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>25,582 km</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Brackenfell (WC)</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/555401152</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_E3E506218</t>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_555401152</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>2025 Big Boy TSR 125</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>R 26,900</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>2,715 km</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>Dome (GP)</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/00E003583</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>2017 Big Boy TSR 250</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>R 14,400</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>R 15,400</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>26,122 km</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>Gqeberha (EC)</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/111213393</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_00E003583</t>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_111213393</t>
         </is>
       </c>
     </row>
@@ -7546,28 +7698,28 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>2023 Big Boy TSR 250</t>
+          <t>2024 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>R 24,900</t>
+          <t>R 8,900</t>
         </is>
       </c>
       <c r="E147" s="4" t="n"/>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>2,135 km</t>
+          <t>40,694 km</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Riverhorse (KZN)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/A5E812682</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/447713059</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -7577,12 +7729,12 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>webuycars_A5E812682</t>
+          <t>webuycars_447713059</t>
         </is>
       </c>
     </row>
@@ -7599,28 +7751,28 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>2024 Big Boy TSR Superlight125</t>
+          <t>2019 Big Boy JNR90 90cc</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>R 21,900</t>
+          <t>R 9,900</t>
         </is>
       </c>
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>3,006 km</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Vereeniging (GP)</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/271C01004</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/JNR90/03B405337</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -7630,12 +7782,12 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>webuycars_271C01004</t>
+          <t>webuycars_03B405337</t>
         </is>
       </c>
     </row>
@@ -7652,28 +7804,28 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy TSR Superlight125</t>
+          <t>2006 Big Boy Expert 125 Expert</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>R 16,900</t>
+          <t>R 8,900</t>
         </is>
       </c>
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>4,183 km</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Vereeniging (GP)</t>
+          <t>Midstream (GP)</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/AA5010103</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Expert/CE4403753</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -7683,65 +7835,69 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>webuycars_AA5010103</t>
+          <t>webuycars_CE4403753</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>2024 Big Boy 125 DLite</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>R 13,900</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>4,060 km</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>Rustenburg (NW)</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/125/B14706796</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>2024 Big Boy Velocity YQ200-2B</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>R 12,400</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>R 13,400</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>26,292 km</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>Germiston (GP)</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity/075500961</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
         <is>
           <t>Big Boy Pacer 200</t>
         </is>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_B14706796</t>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:02</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_075500961</t>
         </is>
       </c>
     </row>
@@ -7758,28 +7914,28 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2023 Big Boy TSR 125</t>
+          <t>2024 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>R 19,900</t>
+          <t>R 10,900</t>
         </is>
       </c>
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>5,702 km</t>
+          <t>29,943 km</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>Dome (GP)</t>
+          <t>Richmond (WC)</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/9EAC15681</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/DF9514668</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -7789,12 +7945,12 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>webuycars_9EAC15681</t>
+          <t>webuycars_DF9514668</t>
         </is>
       </c>
     </row>
@@ -7811,28 +7967,28 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>2022 Big Boy D Lite 125</t>
+          <t>2023 Big Boy TSR 125</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>R 9,400</t>
+          <t>R 17,900</t>
         </is>
       </c>
       <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5,702 km</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>Midstream (GP)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/D Lite/862D10485</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/9EAC15681</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -7842,12 +7998,12 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>webuycars_862D10485</t>
+          <t>webuycars_9EAC15681</t>
         </is>
       </c>
     </row>
@@ -7864,28 +8020,28 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>2019 Big Boy SAM ATV 110 Apollo (monster Crx)</t>
+          <t>2026 Big Boy TSR 250</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>R 11,400</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="n"/>
+          <t>R 25,400</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr"/>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>135 km</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>Montana (GP)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/SAM ATV/EB7402767</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/827909703</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -7895,12 +8051,12 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>webuycars_EB7402767</t>
+          <t>webuycars_827909703</t>
         </is>
       </c>
     </row>
@@ -7917,28 +8073,28 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>2020 Big Boy TSR 125</t>
+          <t>2025 Big Boy TSR 250</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>R 17,400</t>
+          <t>R 26,900</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>9,104 km</t>
+          <t>51 km</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Silver Lakes (GP)</t>
+          <t>Vereeniging (GP)</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/A72011701</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/CEBE03207</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -7948,12 +8104,12 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>webuycars_A72011701</t>
+          <t>webuycars_CEBE03207</t>
         </is>
       </c>
     </row>
@@ -7970,28 +8126,28 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>2022 Big Boy TSR 250</t>
+          <t>2026 Big Boy Velocity Cargo 150</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>R 19,900</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="n"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr"/>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>10,016 km</t>
+          <t>17 km</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>Gqeberha (EC)</t>
+          <t>Mbombela (MP)</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/TSR/315B03737</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/39D711653</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -8001,125 +8157,83 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:02</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>webuycars_315B03737</t>
+          <t>webuycars_39D711653</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100 (5 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>WeBuyCars</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>2024 Big Boy Velocity Cargo 150</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>R 9,900</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>40,694 km</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>2014 Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>R 60,900</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>R 64,900</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>15,724 km</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
         <is>
           <t>Richmond (WC)</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/447713059</t>
-        </is>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_447713059</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>2025 Big Boy Velocity Cargo 150</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>R 14,400</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>9,759 km</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr">
-        <is>
-          <t>Brackenfell (WC)</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/40F311344</t>
-        </is>
-      </c>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_40F311344</t>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Bonneville/60C704431</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Triumph Bonneville T100</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>26-04-2026 08:52:14</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>webuycars_60C704431</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -8129,767 +8243,281 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy 125 Legend 125</t>
+          <t>2012 Triumph Bonneville 865 Bonneville America EFI</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>R 13,900</t>
+          <t>R 44,900</t>
         </is>
       </c>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>11,975 km</t>
+          <t>12,965 km</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>East London (EC)</t>
+          <t>Dome (GP)</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/125/38A210105</t>
+          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Bonneville/C2D803904</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:14</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>webuycars_38A210105</t>
+          <t>webuycars_C2D803904</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy CGL Cgl/ccl/velocity 150</t>
+          <t>2021 Triumph Bonneville SPEED MASTER</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>R 12,900</t>
+          <t>R139,990</t>
         </is>
       </c>
       <c r="E159" s="4" t="n"/>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>12,104 km</t>
+          <t>4,942km</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Gqeberha (EC)</t>
+          <t>Bikeshop Rivonia</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/CGL/6EA211653</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2021-triumph-bonneville-speed-master/</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:14</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>webuycars_6EA211653</t>
+          <t>zabikers_2021-triumph-bonneville-speed-master</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>2025 Big Boy Velocity Cargo 150</t>
+          <t>2003 Triumph Bonneville Speedmaster</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>R 12,900</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n"/>
+          <t>R59,900</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr"/>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>15,410 km</t>
+          <t>17,713km</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>Richmond (WC)</t>
+          <t>Bikeshop Boksburg</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/D76700634</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2003-triumph-bonneville-speedmaster/</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:14</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>webuycars_D76700634</t>
+          <t>zabikers_2003-triumph-bonneville-speedmaster</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>WeBuyCars</t>
+          <t>ZABikers</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>2023 Big Boy 125 Legend 125</t>
+          <t>2017 Triumph BONNEVILLE T120 BOBBER</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>R 14,900</t>
+          <t>R109,950</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>14,929 km</t>
+          <t>22,721km</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Witbank (MP)</t>
+          <t>Harley-Davidson Gold Rand</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/125/E0CC09880</t>
+          <t>https://www.zabikers.co.za/bikes-for-sale/2017-triumph-bonneville-t120-bobber/</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>Big Boy Pacer 200</t>
+          <t>Triumph Bonneville T100</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>31-03-2026 15:14:44</t>
+          <t>26-04-2026 08:52:14</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>webuycars_E0CC09880</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>2024 Big Boy D Lite 125</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>R 12,900</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>16,964 km</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>Midstream (GP)</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/D Lite/04DA01184</t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_04DA01184</t>
+          <t>zabikers_2017-triumph-bonneville-t120-bobber</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>2025 Big Boy Superlight 200</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>R 14,900</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="n"/>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>39,183 km</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>Riverhorse (KZN)</t>
-        </is>
-      </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Superlight/050B11776</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K163" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_050B11776</t>
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>2015 Big Boy Sportflite F35 150</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>R 15,400</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>4,719 km</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>Montana (GP)</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Sportflite/C39209934</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_C39209934</t>
-        </is>
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>Total Listings:</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>2024 Big Boy Superlight 200</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>R 16,900</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>44,295 km</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>Silver Lakes (GP)</t>
-        </is>
-      </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Superlight/498B09809</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_498B09809</t>
-        </is>
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>Bikes Tracked:</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>2025 Big Boy Velocity Cargo 150</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>10,170 km</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>Rustenburg (NW)</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/40AE15178</t>
-        </is>
-      </c>
-      <c r="I166" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_40AE15178</t>
-        </is>
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>Sources:</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>2024 Big Boy Velocity Cargo 150</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>29,943 km</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>Richmond (WC)</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Big Boy/Velocity Cargo/DF9514668</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>Big Boy Pacer 200</t>
-        </is>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:44</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_DF9514668</t>
-        </is>
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>Price Drops Detected:</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100 (3 listings)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>WeBuyCars</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>2014 Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>R 68,900</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>15,724 km</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>Richmond (WC)</t>
-        </is>
-      </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>https://www.webuycars.co.za/buy-a-car/Triumph/Bonneville/60C704431</t>
-        </is>
-      </c>
-      <c r="I169" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:53</t>
-        </is>
-      </c>
-      <c r="K169" s="3" t="inlineStr">
-        <is>
-          <t>webuycars_60C704431</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>2021 Triumph Bonneville SPEED MASTER</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>R139,990</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>4,942km</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Rivonia</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2021-triumph-bonneville-speed-master/</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:53</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2021-triumph-bonneville-speed-master</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>ZABikers</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>2015 Triumph BONNEVILLE NEWCHURCH 865 SPECIAL EDIT...</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>R89,900</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="n"/>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>18,513km</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>Bikeshop Boksburg</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>https://www.zabikers.co.za/bikes-for-sale/2015-triumph-bonneville-newchurch-865-special-edition/</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>Triumph Bonneville T100</t>
-        </is>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>31-03-2026 15:14:53</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr">
-        <is>
-          <t>zabikers_2015-triumph-bonneville-newchurch-865-special-edition</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>Total Listings:</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>Bikes Tracked:</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Sources:</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Price Drops Detected:</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t>Last Updated:</t>
         </is>
       </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>31/03/2026 15:15:06</t>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026 08:52:39</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A168:K168"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A128:K128"/>
+  <mergeCells count="15">
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A79:K79"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A111:K111"/>
+    <mergeCell ref="A156:K156"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A115:K115"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A117:K117"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A67:K67"/>
     <mergeCell ref="A106:K106"/>
-    <mergeCell ref="A123:K123"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="A110:K110"/>
-    <mergeCell ref="A79:K79"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
